--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -143,6 +143,52 @@
   </si>
   <si>
     <t>并发操作，后续考虑java实现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>seqDB-12043</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">查询并使用explain </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全文检索暂不支持explain，暂不考虑实现自动化</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -150,7 +196,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,6 +206,23 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -207,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -216,6 +279,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -702,18 +768,28 @@
         <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="A12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="1"/>

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -8,15 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="正常功能" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="48">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -146,15 +146,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">查询并使用explain </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全文检索暂不支持explain，暂不考虑实现自动化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入多条大长度的全文索引记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>seqDB-12043</t>
     </r>
     <r>
@@ -172,23 +196,32 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">查询并使用explain </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全文检索暂不支持explain，暂不考虑实现自动化</t>
+    <t>seqDB-15757</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入多条15M记录会导致ES服务端异常退出，暂不实现自动化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15449</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ES端已有提交记录，且固定集合中的最小_lid小于等于
+ES端的_lid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试场景需要构造异常（暂无构造手段），暂不实现自动化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15450</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ES端已有提交记录，且固定集合中的最小_lid大于ES端的_lid</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -768,7 +801,7 @@
         <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>21</v>
@@ -776,41 +809,71 @@
     </row>
     <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="D12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="1" t="s">
+    </row>
+    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
+      <c r="A15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="1"/>
@@ -885,5 +948,6 @@
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="63">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -103,10 +103,6 @@
   </si>
   <si>
     <t>大数据量，后续考虑用java实现</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12010</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -222,6 +218,70 @@
   </si>
   <si>
     <t>ES端已有提交记录，且固定集合中的最小_lid大于ES端的_lid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15240</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试场景需要手动重启适配器，暂不实现自动化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JAVA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动化实现类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ES中无提交记录，主备节点会话验证</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">seqDB-14410 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">seqDB-14409 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">重启适配器不影响全文索引功能 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重启ES不影响全文索引功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重启适配器考虑手工验证，不实现自动化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重启ES考虑手工验证，不实现自动化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12010</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -611,16 +671,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="46.875" style="2" customWidth="1"/>
-    <col min="3" max="4" width="21.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="67.125" style="2" customWidth="1"/>
+    <col min="3" max="5" width="21.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="67.125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="1" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -634,10 +694,13 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -651,10 +714,13 @@
         <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -667,11 +733,12 @@
       <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -684,11 +751,12 @@
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -701,11 +769,12 @@
       <c r="D5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="3"/>
+      <c r="F5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -718,11 +787,12 @@
       <c r="D6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="3"/>
+      <c r="F6" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -735,16 +805,19 @@
       <c r="D7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>7</v>
@@ -752,33 +825,37 @@
       <c r="D8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="1" t="s">
+    </row>
+    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>7</v>
@@ -786,143 +863,200 @@
       <c r="D10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="27" customHeight="1">
+      <c r="E10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="27" customHeight="1">
       <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="4" t="s">
+      <c r="E12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="1" t="s">
+    </row>
+    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="E14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="1" t="s">
+    </row>
+    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="E15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
+      <c r="B16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
+      <c r="F17" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="E18" s="1"/>
-    </row>
-    <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="F18" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-    </row>
-    <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
-    </row>
-    <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="69">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -282,6 +282,30 @@
   </si>
   <si>
     <t>seqDB-12010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14411</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选主后不影响全文索引功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JAVA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前JAVA驱动没有选主接口，暂不实现自动化，SEQUOIADBMAINSTREAM-3975</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1019,7 +1043,7 @@
         <v>58</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
@@ -1027,12 +1051,24 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+      <c r="A19" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="1"/>

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="71">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -301,11 +301,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>JAVA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>目前JAVA驱动没有选主接口，暂不实现自动化，SEQUOIADBMAINSTREAM-3975</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14371</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>直连数据节点删除全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>直连数据节点操作有问题，暂不自动化，SEQUOIADBMAINSTREAM-3378、3379</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1064,19 +1072,29 @@
         <v>66</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="1" t="s">
+    </row>
+    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A20" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+      <c r="F20" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="1"/>

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -4,19 +4,22 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="正常功能" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="update无法校验是否同步完，新增测试步骤用例" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">正常功能!$C$1:$C$22</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="69">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -146,10 +149,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>否</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -163,10 +162,6 @@
   </si>
   <si>
     <t>插入多条大长度的全文索引记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -225,10 +220,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>测试场景需要手动重启适配器，暂不实现自动化</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -265,10 +256,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>否</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -293,10 +280,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>否</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -314,6 +297,18 @@
   </si>
   <si>
     <t>直连数据节点操作有问题，暂不自动化，SEQUOIADBMAINSTREAM-3378、3379</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动化用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -395,7 +390,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -409,6 +404,7 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -703,6 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -726,7 +723,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -746,13 +743,13 @@
         <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="3" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -770,7 +767,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="4" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -788,7 +785,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="5" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -806,7 +803,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="6" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -838,7 +835,7 @@
         <v>8</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>20</v>
@@ -846,7 +843,7 @@
     </row>
     <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>22</v>
@@ -858,13 +855,13 @@
         <v>8</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="9" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -896,7 +893,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>30</v>
@@ -913,10 +910,10 @@
         <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>21</v>
@@ -924,179 +921,179 @@
     </row>
     <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="33" customHeight="1">
+      <c r="A14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="1" t="s">
+      <c r="E14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="1" t="s">
+    </row>
+    <row r="15" spans="1:6" ht="39" customHeight="1">
+      <c r="A15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="C15" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="C18" s="1" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1104,7 +1101,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="22" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1113,6 +1110,13 @@
       <c r="F22" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="C1:C22">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="是"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1121,9 +1125,132 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="18.25" customWidth="1"/>
+    <col min="3" max="3" width="17.5" customWidth="1"/>
+    <col min="4" max="4" width="27.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="30" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="30" customHeight="1">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:4" ht="30" customHeight="1">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:4" ht="30" customHeight="1">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:4" ht="30" customHeight="1">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4" ht="30" customHeight="1">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:4" ht="30" customHeight="1">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4" ht="30" customHeight="1">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:4" ht="30" customHeight="1">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:4" ht="30" customHeight="1">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:4" ht="30" customHeight="1">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:4" ht="30" customHeight="1">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:4" ht="30" customHeight="1">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:4" ht="30" customHeight="1">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:4" ht="30" customHeight="1">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:4" ht="30" customHeight="1">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" ht="30" customHeight="1"/>
+    <row r="18" ht="30" customHeight="1"/>
+    <row r="19" ht="30" customHeight="1"/>
+    <row r="20" ht="30" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1"/>
+    <row r="22" ht="30" customHeight="1"/>
+    <row r="23" ht="30" customHeight="1"/>
+    <row r="24" ht="30" customHeight="1"/>
+    <row r="25" ht="30" customHeight="1"/>
+    <row r="26" ht="30" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1"/>
+    <row r="28" ht="30" customHeight="1"/>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="96">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -300,16 +300,97 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>/trunk/testcase_new/story/js/fullText/id_insert_update_15529.js</t>
+  </si>
+  <si>
+    <t>/trunk/testcase_new/story/js/fullText/id_update_es_support_15526.js</t>
+  </si>
+  <si>
+    <t>/trunk/testcase_new/story/js/fullText/update_12026.js</t>
+  </si>
+  <si>
+    <t>/trunk/testcase_new/story/js/fullText/update_12027.js</t>
+  </si>
+  <si>
+    <t>/trunk/testcase_new/story/js/fullText/update_12028.js</t>
+  </si>
+  <si>
+    <t>/trunk/testcase_new/story/js/fullText/update_12029.js</t>
+  </si>
+  <si>
+    <t>/trunk/testcase_new/story/js/fullText/update_14380.js</t>
+  </si>
+  <si>
+    <t>/trunk/testcase_new/story/js/fullText/update_14382.js</t>
+  </si>
+  <si>
+    <t>shardingKey字段为全文索引字段，更新全文索引字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/trunk/testcase_new/story/js/fullText/update_15528.js</t>
+  </si>
+  <si>
+    <t>更新_id及全文索引字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/trunk/testcase_new/story/js/fullText/update_arrays_15776.js</t>
+  </si>
+  <si>
+    <t xml:space="preserve">将全文索引字段为数组类型更新为string类型 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/trunk/testcase_new/story/js/fullText/update_multiple_keys_15781.js</t>
+  </si>
+  <si>
+    <t>自动化用例编号</t>
+  </si>
+  <si>
+    <t>用例名称</t>
+  </si>
+  <si>
     <t>用例类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动化用例编号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/trunk/testcase_new/story/js/fullText/id_insert_update_12008.js</t>
+  </si>
+  <si>
+    <t>指定_id插入/更新记录</t>
+  </si>
+  <si>
+    <t>js</t>
+  </si>
+  <si>
+    <t>在update操作后多加一条插入操作</t>
+  </si>
+  <si>
+    <t>指定_id字段插入记录，并更新</t>
+  </si>
+  <si>
+    <t>seqDB-15526:更新_id字段，类型为支持同步的类型</t>
+  </si>
+  <si>
+    <t>AutoIndexId为false时更新全文索引字段值</t>
+  </si>
+  <si>
+    <t>使用update接口更新全文索引字段</t>
+  </si>
+  <si>
+    <t>更新全文索引字段但不更新值</t>
+  </si>
+  <si>
+    <t>更新记录，使记录中的索引字段存在/不存在</t>
+  </si>
+  <si>
+    <t xml:space="preserve">更新索引字段   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">多键全文索引，部分字段为数组更新为string类型    </t>
   </si>
 </sst>
 </file>
@@ -1128,97 +1209,193 @@
   <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="18.25" customWidth="1"/>
-    <col min="3" max="3" width="17.5" customWidth="1"/>
+    <col min="1" max="1" width="75.625" customWidth="1"/>
+    <col min="2" max="2" width="48.5" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
     <col min="4" max="4" width="27.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="30" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="30" customHeight="1">
+      <c r="A3" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="30" customHeight="1">
+      <c r="A5" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="30" customHeight="1">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-    </row>
-    <row r="3" spans="1:4" ht="30" customHeight="1">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-    </row>
-    <row r="4" spans="1:4" ht="30" customHeight="1">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="1:4" ht="30" customHeight="1">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="B5" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="A6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="7" spans="1:4" ht="30" customHeight="1">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+      <c r="A7" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="A8" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="A9" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="A10" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="A11" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="A12" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="A13" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1">
       <c r="A14" s="5"/>

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="正常功能" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="122">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -300,51 +300,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/trunk/testcase_new/story/js/fullText/id_insert_update_15529.js</t>
-  </si>
-  <si>
-    <t>/trunk/testcase_new/story/js/fullText/id_update_es_support_15526.js</t>
-  </si>
-  <si>
-    <t>/trunk/testcase_new/story/js/fullText/update_12026.js</t>
-  </si>
-  <si>
-    <t>/trunk/testcase_new/story/js/fullText/update_12027.js</t>
-  </si>
-  <si>
-    <t>/trunk/testcase_new/story/js/fullText/update_12028.js</t>
-  </si>
-  <si>
-    <t>/trunk/testcase_new/story/js/fullText/update_12029.js</t>
-  </si>
-  <si>
-    <t>/trunk/testcase_new/story/js/fullText/update_14380.js</t>
-  </si>
-  <si>
-    <t>/trunk/testcase_new/story/js/fullText/update_14382.js</t>
-  </si>
-  <si>
     <t>shardingKey字段为全文索引字段，更新全文索引字段</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/trunk/testcase_new/story/js/fullText/update_15528.js</t>
-  </si>
-  <si>
     <t>更新_id及全文索引字段</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/trunk/testcase_new/story/js/fullText/update_arrays_15776.js</t>
-  </si>
-  <si>
-    <t xml:space="preserve">将全文索引字段为数组类型更新为string类型 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/trunk/testcase_new/story/js/fullText/update_multiple_keys_15781.js</t>
-  </si>
-  <si>
     <t>自动化用例编号</t>
   </si>
   <si>
@@ -357,9 +320,6 @@
     <t>备注</t>
   </si>
   <si>
-    <t>/trunk/testcase_new/story/js/fullText/id_insert_update_12008.js</t>
-  </si>
-  <si>
     <t>指定_id插入/更新记录</t>
   </si>
   <si>
@@ -372,9 +332,6 @@
     <t>指定_id字段插入记录，并更新</t>
   </si>
   <si>
-    <t>seqDB-15526:更新_id字段，类型为支持同步的类型</t>
-  </si>
-  <si>
     <t>AutoIndexId为false时更新全文索引字段值</t>
   </si>
   <si>
@@ -391,6 +348,166 @@
   </si>
   <si>
     <t xml:space="preserve">多键全文索引，部分字段为数组更新为string类型    </t>
+  </si>
+  <si>
+    <t>多键全文索引插入/更新/删除记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在update操作后多加一条插入操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id_insert_update_12008.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id_insert_update_15529.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id_update_es_support_15526.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update_12026.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update_12027.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update_12028.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update_12029.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update_14380.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update_14382.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update_15528.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update_multiple_keys_15781.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3Key_basic_12005.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>basic_11997.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bulk_insert_12001.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>operate_hash_table_records_12013.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update_unique_duplicate_15769.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16Key_basic_12005.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hint_14381.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oneKey_basic_12004.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>operate_range_table_records_12014.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>index_basic_12002.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>find_update_12025.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>create_main_collection_15536.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入/更新/删除包含部分全文索引字段的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用hint更新记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单键全文索引插入/更新/删除记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>range分区表中插入/更新/删除包含全文索引字段的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全文索引字段包含普通索引字段,插入/查询/更新/删除记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用find.update更新全文索引字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新索引字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定集合空间上创建主表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定_id字段插入记录，并更新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非全文索引字段为唯一索引，更新记录使唯一索引重复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新记录，使记录中的索引字段存在/不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动切分的hash分区表中插入/更新/删除包含全文索引字段的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>批量插入/更新/删除记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新_id字段，类型为支持同步的类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -444,7 +561,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -467,11 +584,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -486,6 +614,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1206,227 +1335,393 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="75.625" customWidth="1"/>
-    <col min="2" max="2" width="48.5" customWidth="1"/>
+    <col min="2" max="2" width="56.875" customWidth="1"/>
     <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="4" width="27.375" customWidth="1"/>
+    <col min="4" max="4" width="30.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1">
       <c r="A10" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="30" customHeight="1">
+      <c r="A14" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="30" customHeight="1">
+      <c r="A15" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="30" customHeight="1">
+      <c r="A16" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="30" customHeight="1">
+      <c r="A17" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="30" customHeight="1">
+      <c r="A18" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" t="s">
+        <v>117</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="30" customHeight="1">
+      <c r="A19" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="30" customHeight="1">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:4" ht="30" customHeight="1">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" spans="1:4" ht="30" customHeight="1">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" ht="30" customHeight="1"/>
-    <row r="18" ht="30" customHeight="1"/>
-    <row r="19" ht="30" customHeight="1"/>
-    <row r="20" ht="30" customHeight="1"/>
-    <row r="21" ht="30" customHeight="1"/>
-    <row r="22" ht="30" customHeight="1"/>
-    <row r="23" ht="30" customHeight="1"/>
-    <row r="24" ht="30" customHeight="1"/>
-    <row r="25" ht="30" customHeight="1"/>
-    <row r="26" ht="30" customHeight="1"/>
-    <row r="27" ht="30" customHeight="1"/>
-    <row r="28" ht="30" customHeight="1"/>
+      <c r="B19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="30" customHeight="1">
+      <c r="A20" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="30" customHeight="1">
+      <c r="A21" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="28.5" customHeight="1">
+      <c r="A22" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="27.75" customHeight="1">
+      <c r="A23" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A24" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="31.5" customHeight="1">
+      <c r="A25" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="28.5" customHeight="1">
+      <c r="A26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="29.25" customHeight="1">
+      <c r="A27" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="正常功能" sheetId="1" r:id="rId1"/>
     <sheet name="update无法校验是否同步完，新增测试步骤用例" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
+    <sheet name="自动化用例问题收集" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">正常功能!$C$1:$C$22</definedName>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="125">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -507,6 +507,41 @@
   </si>
   <si>
     <t>更新_id字段，类型为支持同步的类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ES报的异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>all shards failed：
+Failed to execute phase [dfs], all shards failedat org.elasticsearch.action.search.AbstractSearchAsyncAction.onPhaseFailure(AbstractSearchAsyncAction.java:274)at org.elasticsearch.action.search.AbstractSearchAsyncAction.executeNextPhase(AbstractSearchAsyncAction.java:132)at org.elasticsearch.action.search.AbstractSearchAsyncAction.onPhaseDone(AbstractSearchAsyncAction.java:243)at org.elasticsearch.action.search.InitialSearchPhase.onShardFailure(InitialSearchPhase.java:107)at org.elasticsearch.action.search.InitialSearchPhase.access$100(InitialSearchPhase.java:49)at org.elasticsearch.action.search.InitialSearchPhase$2.lambda$onFailure$1(InitialSearchPhase.java:217)at org.elasticsearch.action.search.InitialSearchPhase.maybeFork(InitialSearchPhase.java:171)at org.elasticsearch.action.search.InitialSearchPhase.access$000(InitialSearchPhase.java:49)at org.elasticsearch.action.search.InitialSearchPhase$2.onFailure(InitialSearchPhase.java:217)at org.elasticsearch.action.ActionListenerResponseHandler.handleException(ActionListenerResponseHandler.java:51)at org.elasticsearch.action.search.SearchTransportService$ConnectionCountingHandler.handleException(SearchTransportService.java:531)at org.elasticsearch.transport.TransportService$ContextRestoreResponseHandler.handleException(TransportService.java:1098)at org.elasticsearch.transport.TransportService$DirectResponseChannel.processException(TransportService.java:1191)at org.elasticsearch.transport.TransportService$DirectResponseChannel.sendResponse(TransportService.java:1175)at org.elasticsearch.transport.TaskTransportChannel.sendResponse(TaskTransportChannel.java:66)at org.elasticsearch.action.search.SearchTransportService$5$1.onFailure(SearchTransportService.java:361)at org.elasticsearch.search.SearchService$1.onFailure(SearchService.java:275)at org.elasticsearch.search.SearchService$1.onResponse(SearchService.java:269)at org.elasticsearch.search.SearchService$1.onResponse(SearchService.java:263)at org.elasticsearch.search.SearchService$3.doRun(SearchService.java:1002)at org.elasticsearch.common.util.concurrent.ThreadContext$ContextPreservingAbstractRunnable.doRun(ThreadContext.java:672)at org.elasticsearch.common.util.concurrent.AbstractRunnable.run(AbstractRunnable.java:37)at org.elasticsearch.common.util.concurrent.TimedRunnable.doRun(TimedRunnable.java:41)at org.elasticsearch.common.util.concurrent.AbstractRunnable.run(AbstractRunnable.java:37)at java.util.concurrent.ThreadPoolExecutor.runWorker(ThreadPoolExecutor.java:1149)at java.util.concurrent.ThreadPoolExecutor$Worker.run(ThreadPoolExecutor.java:624)at java.lang.Thread.run(Thread.java:748)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[DEBUG][o.e.h.n.Netty4HttpServerTransport] [9VYdWZo] caught exception while handling client http traffic, closing connection [id: 0xf1f7c7f7, L:/192.168.28.143:9200 - R:/192.168.28.135:59121]
+java.io.IOException: Connection reset by peer
+        at sun.nio.ch.FileDispatcherImpl.read0(Native Method) ~[?:?]
+        at sun.nio.ch.SocketDispatcher.read(SocketDispatcher.java:39) ~[?:?]
+        at sun.nio.ch.IOUtil.readIntoNativeBuffer(IOUtil.java:223) ~[?:?]
+        at sun.nio.ch.IOUtil.read(IOUtil.java:197) ~[?:?]
+        at sun.nio.ch.SocketChannelImpl.read(SocketChannelImpl.java:380) ~[?:?]
+        at io.netty.buffer.PooledHeapByteBuf.setBytes(PooledHeapByteBuf.java:261) ~[netty-buffer-4.1.16.Final.jar:4.1.16.Final]
+        at io.netty.buffer.AbstractByteBuf.writeBytes(AbstractByteBuf.java:1106) ~[netty-buffer-4.1.16.Final.jar:4.1.16.Final]
+        at io.netty.channel.socket.nio.NioSocketChannel.doReadBytes(NioSocketChannel.java:343) ~[netty-transport-4.1.16.Final.jar:4.1.16.Final]
+        at io.netty.channel.nio.AbstractNioByteChannel$NioByteUnsafe.read(AbstractNioByteChannel.java:123) [netty-transport-4.1.16.Final.jar:4.1.16.Final]
+        at io.netty.channel.nio.NioEventLoop.processSelectedKey(NioEventLoop.java:645) [netty-transport-4.1.16.Final.jar:4.1.16.Final]
+        at io.netty.channel.nio.NioEventLoop.processSelectedKeysPlain(NioEventLoop.java:545) [netty-transport-4.1.16.Final.jar:4.1.16.Final]
+        at io.netty.channel.nio.NioEventLoop.processSelectedKeys(NioEventLoop.java:499) [netty-transport-4.1.16.Final.jar:4.1.16.Final]
+        at io.netty.channel.nio.NioEventLoop.run(NioEventLoop.java:459) [netty-transport-4.1.16.Final.jar:4.1.16.Final]
+        at io.netty.util.concurrent.SingleThreadEventExecutor$5.run(SingleThreadEventExecutor.java:858) [netty-common-4.1.16.Final.jar:4.1.16.Final]
+        at java.lang.Thread.run(Thread.java:748) [?:1.8.0_152]
+[2019-03-13T05:19:02,245][DEBUG][o.e.i.s.IndexShard       ] [9VYdWZo] [sys_5931349836228_textindex_14384_group1][0] shard is now inactive
+[2019-03-13T05:19:02,245][DEBUG][o.e.i.s.IndexShard       ] [9VYdWZo] [sys_5931349836228_textindex_14384_group1][1] shard is now inactive
+[2019-03-13T05:19:02,247][DEBUG][o.e.i.s.IndexShard       ] [9VYdWZo] [sys_5931349836228_textindex_14384_group1][2] shard is now inactive
+[2019-03-13T05:19:02,247][DEBUG][o.e.i.s.IndexShard       ] [9VYdWZo] [sys_5931349836228_textindex_14384_group1][3] shard is now inactive
+[2019-03-13T05:19:02,247][DEBUG][o.e.i.s.IndexShard       ] [9VYdWZo] [sys_5931349836228_textindex_14384_group1][4] shard is now inactive
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -599,7 +634,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -615,6 +650,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1730,9 +1770,58 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="28.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="22.5" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="409.5" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+    </row>
+    <row r="3" spans="1:14" ht="381" customHeight="1">
+      <c r="A3" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A3:N3"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="136">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -544,12 +544,55 @@
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve">全量同步时，删除原始集合 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17980</t>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JAVA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-3983</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-18260</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增量同步时，删除原始集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-4093</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>编目节点组切主后，创建全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17979</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -580,6 +623,12 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -634,7 +683,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -655,6 +704,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -950,7 +1000,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16.5" style="2" customWidth="1"/>
@@ -1358,6 +1408,66 @@
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" ht="14.25">
+      <c r="A23" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>133</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="C1:C22">

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="148">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -585,6 +585,54 @@
   </si>
   <si>
     <t>seqDB-17979</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-18265</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常停止编目主节点，选出新主后创建全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JAVA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQUOIADBMAINSTREAM-4326</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17979</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>编目节点组通过选举切主后，创建全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-18266</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常停止两个编目节点后再次重启一个节点，并创建全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-18267</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常停止所有编目节点并重启所有节点，创建全文索引</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -700,11 +748,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1000,7 +1048,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16.5" style="2" customWidth="1"/>
@@ -1410,7 +1458,7 @@
       <c r="F22" s="1"/>
     </row>
     <row r="23" spans="1:6" ht="14.25">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="8" t="s">
         <v>126</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -1463,10 +1511,90 @@
         <v>127</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>129</v>
+        <v>47</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="27">
+      <c r="A28" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1892,40 +2020,40 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="409.5" customHeight="1">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
     </row>
     <row r="3" spans="1:14" ht="381" customHeight="1">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -12,14 +12,14 @@
     <sheet name="自动化用例问题收集" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">正常功能!$C$1:$C$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">正常功能!$C$1:$C$29</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="154">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -633,6 +633,28 @@
   </si>
   <si>
     <t>正常停止所有编目节点并重启所有节点，创建全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">增删改查与truncate并发 </t>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不连接适配器去执行的这个点无法实现自动化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JAVA</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -748,11 +770,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1047,8 +1069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16.5" style="2" customWidth="1"/>
@@ -1097,7 +1118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
+    <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -1115,7 +1136,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
+    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1133,7 +1154,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
+    <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -1151,7 +1172,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
+    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -1209,7 +1230,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
+    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -1441,7 +1462,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
+    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1449,7 +1470,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
+    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1458,152 +1479,168 @@
       <c r="F22" s="1"/>
     </row>
     <row r="23" spans="1:6" ht="14.25">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="1" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="1" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="1" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="1" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="1" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="27">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="1" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="1" t="s">
         <v>141</v>
       </c>
     </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="C1:C22">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="是"/>
-      </filters>
-    </filterColumn>
+  <autoFilter ref="C1:C29">
+    <filterColumn colId="0"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2020,40 +2057,40 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="409.5" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
     </row>
     <row r="3" spans="1:14" ht="381" customHeight="1">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -12,14 +12,14 @@
     <sheet name="自动化用例问题收集" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">正常功能!$C$1:$C$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">正常功能!$C$1:$C$25</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="148">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -545,34 +545,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">全量同步时，删除原始集合 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-17980</t>
-  </si>
-  <si>
     <t>是</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>JAVA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEQUOIADBMAINSTREAM-3983</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-18260</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增量同步时，删除原始集合</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -662,7 +639,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -693,12 +670,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -753,7 +724,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -774,7 +745,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1069,7 +1039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16.5" style="2" customWidth="1"/>
@@ -1462,184 +1432,128 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-    </row>
-    <row r="23" spans="1:6" ht="14.25">
-      <c r="A23" s="10" t="s">
+    <row r="21" spans="1:6">
+      <c r="A21" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>126</v>
       </c>
+      <c r="D21" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="B23" s="1" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="27">
       <c r="A24" s="1" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="D24" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B26" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="27">
-      <c r="A28" s="1" t="s">
+      <c r="C26" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="D26" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>151</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="C1:C29">
+  <autoFilter ref="C1:C25">
     <filterColumn colId="0"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="正常功能" sheetId="1" r:id="rId1"/>
-    <sheet name="update无法校验是否同步完，新增测试步骤用例" sheetId="3" r:id="rId2"/>
-    <sheet name="自动化用例问题收集" sheetId="5" r:id="rId3"/>
+    <sheet name="并发功能" sheetId="7" r:id="rId2"/>
+    <sheet name="update无法校验是否同步完，新增测试步骤用例" sheetId="3" r:id="rId3"/>
+    <sheet name="自动化用例问题收集" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">正常功能!$C$1:$C$25</definedName>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="148">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1039,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16.5" style="2" customWidth="1"/>
@@ -1532,26 +1533,6 @@
         <v>135</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="C1:C25">
     <filterColumn colId="0"/>
@@ -1563,6 +1544,69 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="6" width="30.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="27">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="23.25" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -1957,7 +2001,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="13.5"/>

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -4,15 +4,17 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="正常功能" sheetId="1" r:id="rId1"/>
-    <sheet name="并发功能" sheetId="7" r:id="rId2"/>
-    <sheet name="update无法校验是否同步完，新增测试步骤用例" sheetId="3" r:id="rId3"/>
-    <sheet name="自动化用例问题收集" sheetId="5" r:id="rId4"/>
+    <sheet name="大数据用例" sheetId="9" r:id="rId2"/>
+    <sheet name="并发功能" sheetId="7" r:id="rId3"/>
+    <sheet name="update无法校验是否同步完，新增测试步骤用例" sheetId="3" r:id="rId4"/>
+    <sheet name="自动化用例问题收集" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">并发功能!$F$1:$F$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">正常功能!$C$1:$C$25</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -20,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="269">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,10 +41,6 @@
   </si>
   <si>
     <t>是否实现自动化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15524</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -606,33 +604,478 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>正常停止所有编目节点并重启所有节点，创建全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15798</t>
+  </si>
+  <si>
+    <t>不连接适配器去执行的这个点无法实现自动化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.数据同步到ES的时间暂时定为1个小时，后面需根据性能测试结果调整该参数为5分钟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.全文索引工程目录移动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>seqDB-18267</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>正常停止所有编目节点并重启所有节点，创建全文索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">增删改查与truncate并发 </t>
+    <t>seqDB-15524</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-11981</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-11988</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-11989</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-11990</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-11995</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12018</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12019</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12065</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12066</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14372</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14374</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14376</t>
+  </si>
+  <si>
+    <t>seqDB-14377</t>
+  </si>
+  <si>
+    <t>seqDB-14397</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14398</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14885</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15799</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17980</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-18260</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在非空集合中创建/删除全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hash切分表加入域使用自动切分，创建/删除全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>range切分表中创建/删除全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主子表中创建/删除全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反复重建删除同一个全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主子表中插入/更新/删除包含全文索引字段的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入记录并创建全文索引再执行hash切分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入记录并创建全文索引再执行range切分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入记录并执行hash切分再创建全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入记录并执行range切分再创建全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hash切分表中创建全文索引并切分后再插入记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>range切分表中创建全文索引并切分后再插入记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集合空间上存在全文索引，删除集合空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集合上存在全文索引，删除集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无存量数据，插入记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ES中无提交记录时，插入/修改/删除/查询集合中的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正在处理固定集合中记录，插入/修改/删除/查询集合中的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已处理完固定集合中记录，插入/修改/删除/查询集合中的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集合空间删除后重建相同的全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集合删除后重建相同的全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正在查询固定集合时删除全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主表执行truncate清空记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全量同步时，删除原始集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增量同步时，删除原始集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检视责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检视意见</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘晓璇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尹臻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵小妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卢伟康</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检视是否完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12116</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12117</t>
+  </si>
+  <si>
+    <t>seqDB-12120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12121</t>
+  </si>
+  <si>
+    <t>seqDB-12124</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12128</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14414</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14415</t>
+  </si>
+  <si>
+    <t>seqDB-15579</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15796</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15797</t>
+  </si>
+  <si>
+    <t>seqDB-15825</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15826</t>
+  </si>
+  <si>
+    <t>seqDB-15830</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15831</t>
+  </si>
+  <si>
+    <t>seqDB-15832</t>
+  </si>
+  <si>
+    <t>seqDB-15833</t>
+  </si>
+  <si>
+    <t>seqDB-15834</t>
+  </si>
+  <si>
+    <t>seqDB-15835</t>
+  </si>
+  <si>
+    <t>seqDB-15836</t>
+  </si>
+  <si>
+    <t>seqDB-15837</t>
+  </si>
+  <si>
+    <t>seqDB-15838</t>
+  </si>
+  <si>
+    <t>seqDB-15839</t>
+  </si>
+  <si>
+    <t>seqDB-15840</t>
+  </si>
+  <si>
+    <t>seqDB-15841</t>
+  </si>
+  <si>
+    <t>seqDB-15842</t>
+  </si>
+  <si>
+    <t>seqDB-15843</t>
+  </si>
+  <si>
+    <t>seqDB-15844</t>
+  </si>
+  <si>
+    <t>seqDB-15845</t>
+  </si>
+  <si>
+    <t>seqDB-15846</t>
+  </si>
+  <si>
+    <t>seqDB-15847</t>
+  </si>
+  <si>
+    <t>seqDB-15848</t>
+  </si>
+  <si>
+    <t>seqDB-15849</t>
+  </si>
+  <si>
+    <t>seqDB-15850</t>
+  </si>
+  <si>
+    <t>seqDB-15851</t>
+  </si>
+  <si>
+    <t>seqDB-15852</t>
+  </si>
+  <si>
+    <t>seqDB-15853</t>
+  </si>
+  <si>
+    <t>seqDB-15854</t>
+  </si>
+  <si>
+    <t>seqDB-15855</t>
+  </si>
+  <si>
+    <t>seqDB-15856</t>
+  </si>
+  <si>
+    <t>seqDB-15857</t>
+  </si>
+  <si>
+    <t>seqDB-15858</t>
+  </si>
+  <si>
+    <t>seqDB-15859</t>
+  </si>
+  <si>
+    <t>seqDB-15860</t>
+  </si>
+  <si>
+    <t>seqDB-15874</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15875</t>
+  </si>
+  <si>
+    <t>seqDB-15876</t>
+  </si>
+  <si>
+    <t>seqDB-15877</t>
+  </si>
+  <si>
+    <t>seqDB-15879</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15880</t>
+  </si>
+  <si>
+    <t>seqDB-15881</t>
+  </si>
+  <si>
+    <t>seqDB-18259</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12118</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12125</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12126</t>
+  </si>
+  <si>
+    <t>seqDB-12127</t>
+  </si>
+  <si>
+    <t>seqDB-12129</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12119</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12122</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15871</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15872</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘晓旋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>否</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>不连接适配器去执行的这个点无法实现自动化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>JAVA</t>
+    <t>数据量大</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -725,7 +1168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -742,10 +1185,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1063,7 +1511,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1071,466 +1519,466 @@
     </row>
     <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="C3" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="C4" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="C5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="C6" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="C9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="C10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="27" customHeight="1">
       <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="C11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="33" customHeight="1">
       <c r="A14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="39" customHeight="1">
       <c r="A15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="C15" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="C17" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="C20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="C23" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="27">
       <c r="A24" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="C24" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1545,13 +1993,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="6" width="30.625" customWidth="1"/>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
+    <col min="2" max="2" width="46.375" customWidth="1"/>
+    <col min="3" max="3" width="20.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="5" max="5" width="35.625" customWidth="1"/>
+    <col min="6" max="6" width="30.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27">
+    <row r="1" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1559,54 +2012,1170 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+    </row>
+    <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A3" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A4" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+    </row>
+    <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A5" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+    </row>
+    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A7" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+    </row>
+    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A8" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A9" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A10" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A11" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A12" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A13" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A14" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+    </row>
+    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A15" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A16" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+    </row>
+    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A17" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A18" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A19" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A20" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A21" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A22" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A23" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+    </row>
+    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A24" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+    </row>
+    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A25" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I64"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="14.75" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="15.25" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="5" max="7" width="16.5" style="8" customWidth="1"/>
+    <col min="8" max="9" width="30.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>196</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="23.25" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+    <row r="2" spans="1:9">
+      <c r="A2" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="27">
+      <c r="A13" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>202</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="F1:F64"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -1619,380 +3188,380 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="30" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C20" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="28.5" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C22" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="27.75" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C23" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="29.25" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C24" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="31.5" customHeight="1">
       <c r="A25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C25" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="28.5" customHeight="1">
       <c r="A26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C26" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="29.25" customHeight="1">
       <c r="A27" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2001,54 +3570,64 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="28.125" customWidth="1"/>
+    <col min="1" max="1" width="84.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22.5" customHeight="1">
       <c r="A1" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="409.5" customHeight="1">
+      <c r="A2" s="9" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="409.5" customHeight="1">
-      <c r="A2" s="8" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+    </row>
+    <row r="3" spans="1:14" ht="381" customHeight="1">
+      <c r="A3" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-    </row>
-    <row r="3" spans="1:14" ht="381" customHeight="1">
-      <c r="A3" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="8" t="s">
+        <v>143</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="270">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -843,6 +843,9 @@
   <si>
     <t>赵小妮</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
   </si>
   <si>
     <t>黄晓妮</t>
@@ -2018,7 +2021,7 @@
         <v>194</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>195</v>
@@ -2035,7 +2038,7 @@
         <v>197</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
@@ -2051,7 +2054,7 @@
         <v>198</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
@@ -2067,7 +2070,7 @@
         <v>198</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -2083,7 +2086,7 @@
         <v>197</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -2099,7 +2102,7 @@
         <v>197</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -2115,7 +2118,7 @@
         <v>197</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -2131,7 +2134,7 @@
         <v>197</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -2147,7 +2150,7 @@
         <v>197</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -2163,7 +2166,7 @@
         <v>197</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -2179,7 +2182,7 @@
         <v>197</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -2195,7 +2198,7 @@
         <v>199</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -2211,7 +2214,7 @@
         <v>199</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -2227,7 +2230,7 @@
         <v>198</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -2243,7 +2246,7 @@
         <v>198</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
@@ -2259,7 +2262,7 @@
         <v>198</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
@@ -2275,7 +2278,7 @@
         <v>197</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
@@ -2291,7 +2294,7 @@
         <v>197</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
@@ -2307,7 +2310,7 @@
         <v>197</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -2323,7 +2326,7 @@
         <v>197</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -2339,7 +2342,7 @@
         <v>197</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -2355,7 +2358,7 @@
         <v>198</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -2371,7 +2374,7 @@
         <v>198</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -2387,7 +2390,7 @@
         <v>198</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -2403,7 +2406,7 @@
         <v>198</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -2416,6 +2419,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I64"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -2447,7 +2451,7 @@
         <v>194</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>195</v>
@@ -2456,9 +2460,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" hidden="1">
       <c r="A2" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2467,132 +2471,132 @@
         <v>198</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" hidden="1">
       <c r="A3" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>198</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" hidden="1">
       <c r="A4" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>198</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" hidden="1">
       <c r="A5" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>198</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" hidden="1">
       <c r="A6" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>198</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" hidden="1">
       <c r="A7" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>198</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" hidden="1">
       <c r="A8" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>198</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" hidden="1">
       <c r="A9" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>198</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" hidden="1">
       <c r="A10" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>198</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>266</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="27">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="27" hidden="1">
       <c r="A13" s="8" t="s">
         <v>140</v>
       </c>
@@ -2600,575 +2604,581 @@
         <v>198</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" hidden="1">
       <c r="A14" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>198</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" hidden="1">
       <c r="A15" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>198</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" hidden="1">
       <c r="A16" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>198</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" hidden="1">
       <c r="A17" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>198</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" hidden="1">
       <c r="A18" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>198</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" hidden="1">
       <c r="A19" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>198</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" hidden="1">
       <c r="A20" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" hidden="1">
       <c r="A21" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" hidden="1">
       <c r="A22" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" hidden="1">
       <c r="A23" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" hidden="1">
       <c r="A24" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" hidden="1">
       <c r="A25" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" hidden="1">
       <c r="A26" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" hidden="1">
       <c r="A27" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" hidden="1">
       <c r="A28" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" hidden="1">
       <c r="A29" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" hidden="1">
       <c r="A30" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" hidden="1">
       <c r="A31" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" hidden="1">
       <c r="A32" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" hidden="1">
       <c r="A33" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" hidden="1">
       <c r="A34" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>266</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" hidden="1">
       <c r="A37" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" hidden="1">
       <c r="A38" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" hidden="1">
       <c r="A39" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" hidden="1">
       <c r="A40" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" hidden="1">
       <c r="A41" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>266</v>
+        <v>202</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>266</v>
+        <v>202</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>266</v>
+        <v>202</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>266</v>
+        <v>202</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>266</v>
+        <v>202</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>266</v>
+        <v>203</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" hidden="1">
       <c r="A49" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" hidden="1">
       <c r="A50" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" hidden="1">
       <c r="A51" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" hidden="1">
       <c r="A52" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" hidden="1">
       <c r="A53" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" hidden="1">
       <c r="A54" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>266</v>
+        <v>203</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F56" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" hidden="1">
+      <c r="A57" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" hidden="1">
+      <c r="A58" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" hidden="1">
+      <c r="A59" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" hidden="1">
+      <c r="A60" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" hidden="1">
+      <c r="A61" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" hidden="1">
+      <c r="A62" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" hidden="1">
+      <c r="A63" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" hidden="1">
+      <c r="A64" s="8" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="8" t="s">
-        <v>265</v>
-      </c>
       <c r="E64" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="F1:F64"/>
+  <autoFilter ref="F1:F64">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="刘晓旋"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="正常功能" sheetId="1" r:id="rId1"/>
@@ -15,6 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">并发功能!$F$1:$F$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">大数据用例!$A$1:$F$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">正常功能!$C$1:$C$25</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="281">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -725,6 +726,295 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>正在查询固定集合时删除全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主表执行truncate清空记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全量同步时，删除原始集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增量同步时，删除原始集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检视责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检视意见</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘晓璇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尹臻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵小妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卢伟康</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检视是否完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12116</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12117</t>
+  </si>
+  <si>
+    <t>seqDB-12120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12121</t>
+  </si>
+  <si>
+    <t>seqDB-12124</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12128</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14414</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14415</t>
+  </si>
+  <si>
+    <t>seqDB-15579</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15796</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15797</t>
+  </si>
+  <si>
+    <t>seqDB-15825</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15826</t>
+  </si>
+  <si>
+    <t>seqDB-15830</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15831</t>
+  </si>
+  <si>
+    <t>seqDB-15832</t>
+  </si>
+  <si>
+    <t>seqDB-15833</t>
+  </si>
+  <si>
+    <t>seqDB-15834</t>
+  </si>
+  <si>
+    <t>seqDB-15835</t>
+  </si>
+  <si>
+    <t>seqDB-15836</t>
+  </si>
+  <si>
+    <t>seqDB-15837</t>
+  </si>
+  <si>
+    <t>seqDB-15838</t>
+  </si>
+  <si>
+    <t>seqDB-15839</t>
+  </si>
+  <si>
+    <t>seqDB-15840</t>
+  </si>
+  <si>
+    <t>seqDB-15841</t>
+  </si>
+  <si>
+    <t>seqDB-15842</t>
+  </si>
+  <si>
+    <t>seqDB-15843</t>
+  </si>
+  <si>
+    <t>seqDB-15844</t>
+  </si>
+  <si>
+    <t>seqDB-15845</t>
+  </si>
+  <si>
+    <t>seqDB-15846</t>
+  </si>
+  <si>
+    <t>seqDB-15847</t>
+  </si>
+  <si>
+    <t>seqDB-15848</t>
+  </si>
+  <si>
+    <t>seqDB-15849</t>
+  </si>
+  <si>
+    <t>seqDB-15850</t>
+  </si>
+  <si>
+    <t>seqDB-15851</t>
+  </si>
+  <si>
+    <t>seqDB-15852</t>
+  </si>
+  <si>
+    <t>seqDB-15853</t>
+  </si>
+  <si>
+    <t>seqDB-15854</t>
+  </si>
+  <si>
+    <t>seqDB-15855</t>
+  </si>
+  <si>
+    <t>seqDB-15856</t>
+  </si>
+  <si>
+    <t>seqDB-15857</t>
+  </si>
+  <si>
+    <t>seqDB-15858</t>
+  </si>
+  <si>
+    <t>seqDB-15859</t>
+  </si>
+  <si>
+    <t>seqDB-15860</t>
+  </si>
+  <si>
+    <t>seqDB-15874</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15875</t>
+  </si>
+  <si>
+    <t>seqDB-15876</t>
+  </si>
+  <si>
+    <t>seqDB-15877</t>
+  </si>
+  <si>
+    <t>seqDB-15879</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15880</t>
+  </si>
+  <si>
+    <t>seqDB-15881</t>
+  </si>
+  <si>
+    <t>seqDB-18259</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12118</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12125</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12126</t>
+  </si>
+  <si>
+    <t>seqDB-12127</t>
+  </si>
+  <si>
+    <t>seqDB-12129</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12119</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12122</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15871</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15872</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘晓旋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据量大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘晓璇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>在非空集合中创建/删除全文索引</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -805,280 +1095,51 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>正在查询固定集合时删除全文索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主表执行truncate清空记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全量同步时，删除原始集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增量同步时，删除原始集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检视责任人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检视意见</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例责任人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘晓璇</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>尹臻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>赵小妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄晓妮</t>
-  </si>
-  <si>
-    <t>黄晓妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>赵育</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>卢伟康</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检视是否完成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12116</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12117</t>
-  </si>
-  <si>
-    <t>seqDB-12120</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12121</t>
-  </si>
-  <si>
-    <t>seqDB-12124</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12128</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-14414</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-14415</t>
-  </si>
-  <si>
-    <t>seqDB-15579</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15796</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15797</t>
-  </si>
-  <si>
-    <t>seqDB-15825</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15826</t>
-  </si>
-  <si>
-    <t>seqDB-15830</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15831</t>
-  </si>
-  <si>
-    <t>seqDB-15832</t>
-  </si>
-  <si>
-    <t>seqDB-15833</t>
-  </si>
-  <si>
-    <t>seqDB-15834</t>
-  </si>
-  <si>
-    <t>seqDB-15835</t>
-  </si>
-  <si>
-    <t>seqDB-15836</t>
-  </si>
-  <si>
-    <t>seqDB-15837</t>
-  </si>
-  <si>
-    <t>seqDB-15838</t>
-  </si>
-  <si>
-    <t>seqDB-15839</t>
-  </si>
-  <si>
-    <t>seqDB-15840</t>
-  </si>
-  <si>
-    <t>seqDB-15841</t>
-  </si>
-  <si>
-    <t>seqDB-15842</t>
-  </si>
-  <si>
-    <t>seqDB-15843</t>
-  </si>
-  <si>
-    <t>seqDB-15844</t>
-  </si>
-  <si>
-    <t>seqDB-15845</t>
-  </si>
-  <si>
-    <t>seqDB-15846</t>
-  </si>
-  <si>
-    <t>seqDB-15847</t>
-  </si>
-  <si>
-    <t>seqDB-15848</t>
-  </si>
-  <si>
-    <t>seqDB-15849</t>
-  </si>
-  <si>
-    <t>seqDB-15850</t>
-  </si>
-  <si>
-    <t>seqDB-15851</t>
-  </si>
-  <si>
-    <t>seqDB-15852</t>
-  </si>
-  <si>
-    <t>seqDB-15853</t>
-  </si>
-  <si>
-    <t>seqDB-15854</t>
-  </si>
-  <si>
-    <t>seqDB-15855</t>
-  </si>
-  <si>
-    <t>seqDB-15856</t>
-  </si>
-  <si>
-    <t>seqDB-15857</t>
-  </si>
-  <si>
-    <t>seqDB-15858</t>
-  </si>
-  <si>
-    <t>seqDB-15859</t>
-  </si>
-  <si>
-    <t>seqDB-15860</t>
-  </si>
-  <si>
-    <t>seqDB-15874</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15875</t>
-  </si>
-  <si>
-    <t>seqDB-15876</t>
-  </si>
-  <si>
-    <t>seqDB-15877</t>
-  </si>
-  <si>
-    <t>seqDB-15879</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15880</t>
-  </si>
-  <si>
-    <t>seqDB-15881</t>
-  </si>
-  <si>
-    <t>seqDB-18259</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12123</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12118</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12125</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12126</t>
-  </si>
-  <si>
-    <t>seqDB-12127</t>
-  </si>
-  <si>
-    <t>seqDB-12129</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12119</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12122</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15871</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15872</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘晓旋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据量大</t>
+    <t>1、文本用例和自动化用例检查点不完整，缺少：固定集合与原集合数据一致性检查、节点间数据一致性检查。
+2、test中的db.close建议在try里面新建连接，如果多个步骤使用建议放到finally关闭
+3、存在db连接未关闭告警</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、多个未使用的import没有清掉
+2、1个test里面包含3个独立的测试点，每个测试点又包含多个小的测试点（创建、删除索引），导致test里面代码量大，测试点不够清晰。建议：分3个test，每个test预置插数据的步骤放到beforeMethod。
+3、代码注释太多，有些1行代码1行注释，建议删除部分注释或将部分注释整合（如create index and check results）
+4、部分代码多且多次调用的建议另写私有方法调用
+5、insertData没有特殊考虑建议使用公共方法FullTextDBUtils.insertData
+6、sdb、esClient关闭连接统一加上 !=null 的判断
+7、teardown里面的连接需要放到finally里面，否则前面有步骤执行失败不会走到关闭连接，连接残留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、判断组个数统一用CommLib.OneGroupMode
+2、1个组上多个子表的场景没有覆盖到
+3、插入数据和创建索引测试点有些乱，见用例批注
+4、插入数据建议改为使用公共方法FullTextDBUtils.insertData
+5、不需要先删除所有子表再删主表，删除主表会同时删除主表下挂载的子表（主子表公共问题）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、split切分后没有分别检查源组和目标组数据（只检查了数据同步到ES即节点间数据一致性，不能确定是否有切分及切分后的结果）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同 12016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、test里面包含一大堆准备工作的步骤（挂载子表、创建/获取全文索引），实际测试点是插入/更新/删除记录，准备工作建议放到setUp（很多用例都要类似这种问题，请排查修改）
+2、检查结果不完整，如删除没有检查数据不存在、更新没有检查数据是否已被更新正确、插入没有检查插入的数据存在且正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、代码逻辑不够清晰，建议优化，见用例批注
+2、很多db.close不规范的哦（公共问题）
+3、检查结果同12015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、代码貌似跟 14374 没区别（一个时es没数据，一个时数据处理中，但是代码层面看不出区别，且测试点怎么保证有测到点上？）
+2、其他同14374</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1171,7 +1232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1197,12 +1258,87 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1214,7 +1350,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1996,18 +2132,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F25"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.375" customWidth="1"/>
-    <col min="2" max="2" width="46.375" customWidth="1"/>
+    <col min="2" max="2" width="33.875" customWidth="1"/>
     <col min="3" max="3" width="20.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="17.5" customWidth="1"/>
-    <col min="5" max="5" width="35.625" customWidth="1"/>
-    <col min="6" max="6" width="30.625" customWidth="1"/>
+    <col min="4" max="4" width="33.375" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="6" max="6" width="84.625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="1" spans="1:6" ht="36" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2015,405 +2152,436 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="10" customFormat="1" ht="36.75" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>170</v>
+      <c r="B2" s="15" t="s">
+        <v>253</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>197</v>
+        <v>250</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>201</v>
+        <v>251</v>
       </c>
       <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-    </row>
-    <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="F2" s="15" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
       <c r="A3" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>171</v>
+      <c r="B3" s="15" t="s">
+        <v>254</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="4" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
       <c r="A4" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>172</v>
+      <c r="B4" s="15" t="s">
+        <v>255</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="5" spans="1:6" s="10" customFormat="1" ht="81">
       <c r="A5" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>173</v>
+      <c r="B5" s="15" t="s">
+        <v>256</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="F5" s="15" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="10" customFormat="1" ht="67.5">
       <c r="A6" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>174</v>
+      <c r="B6" s="15" t="s">
+        <v>257</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="F6" s="15" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="10" customFormat="1" ht="67.5">
       <c r="A7" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>175</v>
+      <c r="B7" s="15" t="s">
+        <v>258</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="F7" s="15" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="10" customFormat="1" ht="27">
       <c r="A8" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>176</v>
+      <c r="B8" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>202</v>
+        <v>177</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>182</v>
       </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="F8" s="15" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="10" customFormat="1" ht="27">
       <c r="A9" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>202</v>
+      <c r="D9" s="5" t="s">
+        <v>182</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="F9" s="15" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="10" customFormat="1" ht="27">
       <c r="A10" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>178</v>
+      <c r="B10" s="15" t="s">
+        <v>261</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>202</v>
+        <v>177</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>182</v>
       </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="F10" s="15" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="10" customFormat="1" ht="27">
       <c r="A11" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>179</v>
+      <c r="B11" s="15" t="s">
+        <v>262</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>202</v>
+        <v>177</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>182</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="F11" s="15" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
       <c r="A12" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>199</v>
+      <c r="B12" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>179</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="13" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
       <c r="A13" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>199</v>
+      <c r="B13" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>179</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>201</v>
+        <v>252</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
     </row>
-    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="14" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
       <c r="A14" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>182</v>
+      <c r="B14" s="15" t="s">
+        <v>265</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
     </row>
-    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="15" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
       <c r="A15" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>183</v>
+      <c r="B15" s="15" t="s">
+        <v>266</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
     </row>
-    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="16" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
       <c r="A16" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>184</v>
+      <c r="B16" s="15" t="s">
+        <v>267</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
     </row>
-    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="17" spans="1:6" s="10" customFormat="1" ht="40.5">
       <c r="A17" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>185</v>
+      <c r="B17" s="15" t="s">
+        <v>268</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-    </row>
-    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="F17" s="15" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="10" customFormat="1" ht="40.5">
       <c r="A18" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>186</v>
+      <c r="B18" s="15" t="s">
+        <v>269</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="F18" s="15" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="10" customFormat="1" ht="27">
       <c r="A19" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>187</v>
+      <c r="B19" s="15" t="s">
+        <v>270</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-    </row>
-    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="F19" s="15"/>
+    </row>
+    <row r="20" spans="1:6" s="10" customFormat="1">
       <c r="A20" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>188</v>
+      <c r="B20" s="15" t="s">
+        <v>271</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="F20" s="15"/>
+    </row>
+    <row r="21" spans="1:6" s="10" customFormat="1">
       <c r="A21" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>189</v>
+      <c r="B21" s="15" t="s">
+        <v>272</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-    </row>
-    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="F21" s="15"/>
+    </row>
+    <row r="22" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
       <c r="A22" s="5" t="s">
         <v>166</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
     </row>
-    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="23" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
       <c r="A23" s="5" t="s">
         <v>167</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
     </row>
-    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="24" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
       <c r="A24" s="5" t="s">
         <v>168</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
     </row>
-    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="25" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
       <c r="A25" s="5" t="s">
         <v>169</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
     </row>
+    <row r="28" spans="1:6">
+      <c r="B28" s="9"/>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:F25">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="刘晓璇"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2445,16 +2613,16 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>3</v>
@@ -2462,16 +2630,16 @@
     </row>
     <row r="2" spans="1:9" hidden="1">
       <c r="A2" s="8" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="8" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -2479,121 +2647,121 @@
     </row>
     <row r="3" spans="1:9" hidden="1">
       <c r="A3" s="8" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:9" hidden="1">
       <c r="A4" s="8" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:9" hidden="1">
       <c r="A5" s="8" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:9" hidden="1">
       <c r="A6" s="8" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:9" hidden="1">
       <c r="A7" s="8" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:9" hidden="1">
       <c r="A8" s="8" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:9" hidden="1">
       <c r="A9" s="8" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:9" hidden="1">
       <c r="A10" s="8" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="8" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="8" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="27" hidden="1">
@@ -2601,10 +2769,10 @@
         <v>140</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>141</v>
@@ -2612,570 +2780,570 @@
     </row>
     <row r="14" spans="1:9" hidden="1">
       <c r="A14" s="8" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="E14" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" hidden="1">
-      <c r="A15" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="E16" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="8" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" hidden="1">
-      <c r="A16" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" hidden="1">
-      <c r="A17" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" hidden="1">
-      <c r="A18" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" hidden="1">
-      <c r="A19" s="8" t="s">
-        <v>221</v>
-      </c>
       <c r="E19" s="8" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:6" hidden="1">
       <c r="A20" s="8" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:6" hidden="1">
       <c r="A21" s="8" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22" spans="1:6" hidden="1">
       <c r="A22" s="8" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:6" hidden="1">
       <c r="A23" s="8" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" hidden="1">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="8" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" hidden="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="8" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" hidden="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="8" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" hidden="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="8" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" hidden="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="8" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:6" hidden="1">
       <c r="A29" s="8" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="30" spans="1:6" hidden="1">
       <c r="A30" s="8" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" hidden="1">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="8" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" hidden="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="8" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" hidden="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="8" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" hidden="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="8" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="8" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="8" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row r="37" spans="1:6" hidden="1">
       <c r="A37" s="8" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
     </row>
     <row r="38" spans="1:6" hidden="1">
       <c r="A38" s="8" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="1:6" hidden="1">
       <c r="A39" s="8" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
     </row>
     <row r="40" spans="1:6" hidden="1">
       <c r="A40" s="8" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
     </row>
     <row r="41" spans="1:6" hidden="1">
       <c r="A41" s="8" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" hidden="1">
       <c r="A42" s="8" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" hidden="1">
       <c r="A43" s="8" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" hidden="1">
       <c r="A44" s="8" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" hidden="1">
       <c r="A45" s="8" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" hidden="1">
       <c r="A46" s="8" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" hidden="1">
       <c r="A47" s="8" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" hidden="1">
       <c r="A48" s="8" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
     </row>
     <row r="49" spans="1:6" hidden="1">
       <c r="A49" s="8" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="50" spans="1:6" hidden="1">
       <c r="A50" s="8" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="51" spans="1:6" hidden="1">
       <c r="A51" s="8" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52" spans="1:6" hidden="1">
       <c r="A52" s="8" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="53" spans="1:6" hidden="1">
       <c r="A53" s="8" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="54" spans="1:6" hidden="1">
       <c r="A54" s="8" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" hidden="1">
       <c r="A55" s="8" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" hidden="1">
       <c r="A56" s="8" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" hidden="1">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" s="8" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" hidden="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58" s="8" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
     </row>
     <row r="59" spans="1:6" hidden="1">
       <c r="A59" s="8" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="60" spans="1:6" hidden="1">
       <c r="A60" s="8" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" hidden="1">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61" s="8" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" hidden="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62" s="8" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
     </row>
     <row r="63" spans="1:6" hidden="1">
       <c r="A63" s="8" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
     </row>
     <row r="64" spans="1:6" hidden="1">
       <c r="A64" s="8" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="F1:F64">
     <filterColumn colId="0">
       <filters>
-        <filter val="刘晓旋"/>
+        <filter val="黄晓妮"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -3594,40 +3762,40 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="409.5" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
     </row>
     <row r="3" spans="1:14" ht="381" customHeight="1">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="8" t="s">

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="286">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1119,14 +1119,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、split切分后没有分别检查源组和目标组数据（只检查了数据同步到ES即节点间数据一致性，不能确定是否有切分及切分后的结果）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同 12016</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、test里面包含一大堆准备工作的步骤（挂载子表、创建/获取全文索引），实际测试点是插入/更新/删除记录，准备工作建议放到setUp（很多用例都要类似这种问题，请排查修改）
 2、检查结果不完整，如删除没有检查数据不存在、更新没有检查数据是否已被更新正确、插入没有检查插入的数据存在且正确</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1140,6 +1132,43 @@
   <si>
     <t>1、代码貌似跟 14374 没区别（一个时es没数据，一个时数据处理中，但是代码层面看不出区别，且测试点怎么保证有测到点上？）
 2、其他同14374</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.切分表需要分组校验数据量，统一新增公共方法进行校验
+2.teardown里面统一校验下固定集合是否残留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.切分表需要分组校验数据量，统一新增公共方法进行校验
+2.注释部分文件名为手工用例编号及标题
+3.teardown里面统一校验下固定集合是否残留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.truncate集合的时候，需要修改调用修改后的公共方法
+2.teardown里面统一校验下固定集合、ES是否残留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.定义的集合名字需修改成规范的
+2.删除全文索引的时候需要规避-190，避免用例随机失败
+3.删除全文索引后，需要检查固定集合主备节点均无残留,遗漏检测点
+4.上下文无残留，需要确认下是否可以校验；
+5.teardown里面统一校验下固定集合、ES是否残留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.truncate集合的时候，需要修改调用修改后的公共方法
+2.teardown里面统一校验下固定集合、ES是否残留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与用例11981重复，对应手工用例及自动化用例需删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与用例14372重复，对应手工用例及自动化用例需删除</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1258,87 +1287,19 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -1350,7 +1311,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2164,11 +2125,11 @@
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="10" customFormat="1" ht="36.75" customHeight="1">
+    <row r="2" spans="1:6" s="10" customFormat="1" ht="36.75" hidden="1" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="13" t="s">
         <v>253</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -2178,7 +2139,7 @@
         <v>251</v>
       </c>
       <c r="E2" s="5"/>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="13" t="s">
         <v>274</v>
       </c>
     </row>
@@ -2186,7 +2147,7 @@
       <c r="A3" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>254</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -2198,11 +2159,11 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
+    <row r="4" spans="1:6" s="10" customFormat="1" hidden="1">
       <c r="A4" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="13" t="s">
         <v>255</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -2214,11 +2175,11 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="1:6" s="10" customFormat="1" ht="81">
+    <row r="5" spans="1:6" s="10" customFormat="1" ht="67.5" hidden="1">
       <c r="A5" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="13" t="s">
         <v>256</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -2228,15 +2189,15 @@
         <v>181</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="13" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="10" customFormat="1" ht="67.5">
+    <row r="6" spans="1:6" s="10" customFormat="1" ht="54" hidden="1">
       <c r="A6" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="13" t="s">
         <v>257</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -2246,15 +2207,15 @@
         <v>183</v>
       </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="13" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="10" customFormat="1" ht="67.5">
+    <row r="7" spans="1:6" s="10" customFormat="1" ht="54" hidden="1">
       <c r="A7" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="13" t="s">
         <v>258</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -2264,15 +2225,15 @@
         <v>183</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="15" t="s">
-        <v>278</v>
+      <c r="F7" s="13" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="10" customFormat="1" ht="27">
       <c r="A8" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="13" t="s">
         <v>259</v>
       </c>
       <c r="C8" s="5" t="s">
@@ -2282,15 +2243,15 @@
         <v>182</v>
       </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="15" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="10" customFormat="1" ht="27">
+      <c r="F8" s="13" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="10" customFormat="1" ht="40.5">
       <c r="A9" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="13" t="s">
         <v>260</v>
       </c>
       <c r="C9" s="5" t="s">
@@ -2300,15 +2261,15 @@
         <v>182</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="15" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="10" customFormat="1" ht="27">
+      <c r="F9" s="13" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="10" customFormat="1" ht="40.5">
       <c r="A10" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="13" t="s">
         <v>261</v>
       </c>
       <c r="C10" s="5" t="s">
@@ -2318,15 +2279,15 @@
         <v>182</v>
       </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="15" t="s">
-        <v>277</v>
+      <c r="F10" s="13" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="10" customFormat="1" ht="27">
       <c r="A11" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="13" t="s">
         <v>262</v>
       </c>
       <c r="C11" s="5" t="s">
@@ -2336,15 +2297,15 @@
         <v>182</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="15" t="s">
-        <v>277</v>
+      <c r="F11" s="13" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
       <c r="A12" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="13" t="s">
         <v>263</v>
       </c>
       <c r="C12" s="5" t="s">
@@ -2360,7 +2321,7 @@
       <c r="A13" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="13" t="s">
         <v>264</v>
       </c>
       <c r="C13" s="5" t="s">
@@ -2376,7 +2337,7 @@
       <c r="A14" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="13" t="s">
         <v>265</v>
       </c>
       <c r="C14" s="5" t="s">
@@ -2388,11 +2349,11 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
     </row>
-    <row r="15" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
+    <row r="15" spans="1:6" s="10" customFormat="1" hidden="1">
       <c r="A15" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="13" t="s">
         <v>266</v>
       </c>
       <c r="C15" s="5" t="s">
@@ -2404,11 +2365,11 @@
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
     </row>
-    <row r="16" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
+    <row r="16" spans="1:6" s="10" customFormat="1" hidden="1">
       <c r="A16" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="13" t="s">
         <v>267</v>
       </c>
       <c r="C16" s="5" t="s">
@@ -2420,11 +2381,11 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
     </row>
-    <row r="17" spans="1:6" s="10" customFormat="1" ht="40.5">
+    <row r="17" spans="1:6" s="10" customFormat="1" ht="40.5" hidden="1">
       <c r="A17" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="13" t="s">
         <v>268</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -2434,15 +2395,15 @@
         <v>183</v>
       </c>
       <c r="E17" s="5"/>
-      <c r="F17" s="15" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="10" customFormat="1" ht="40.5">
+      <c r="F17" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="10" customFormat="1" ht="40.5" hidden="1">
       <c r="A18" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="13" t="s">
         <v>269</v>
       </c>
       <c r="C18" s="5" t="s">
@@ -2452,15 +2413,15 @@
         <v>183</v>
       </c>
       <c r="E18" s="5"/>
-      <c r="F18" s="15" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="10" customFormat="1" ht="27">
+      <c r="F18" s="13" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
       <c r="A19" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="13" t="s">
         <v>270</v>
       </c>
       <c r="C19" s="5" t="s">
@@ -2470,13 +2431,13 @@
         <v>183</v>
       </c>
       <c r="E19" s="5"/>
-      <c r="F19" s="15"/>
-    </row>
-    <row r="20" spans="1:6" s="10" customFormat="1">
+      <c r="F19" s="13"/>
+    </row>
+    <row r="20" spans="1:6" s="10" customFormat="1" hidden="1">
       <c r="A20" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="13" t="s">
         <v>271</v>
       </c>
       <c r="C20" s="5" t="s">
@@ -2486,13 +2447,13 @@
         <v>181</v>
       </c>
       <c r="E20" s="5"/>
-      <c r="F20" s="15"/>
-    </row>
-    <row r="21" spans="1:6" s="10" customFormat="1">
+      <c r="F20" s="13"/>
+    </row>
+    <row r="21" spans="1:6" s="10" customFormat="1" hidden="1">
       <c r="A21" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="13" t="s">
         <v>272</v>
       </c>
       <c r="C21" s="5" t="s">
@@ -2502,9 +2463,9 @@
         <v>181</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="F21" s="15"/>
-    </row>
-    <row r="22" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
+      <c r="F21" s="13"/>
+    </row>
+    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="5" t="s">
         <v>166</v>
       </c>
@@ -2518,9 +2479,11 @@
         <v>182</v>
       </c>
       <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
+      <c r="F22" s="13" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A23" s="5" t="s">
         <v>167</v>
       </c>
@@ -2534,9 +2497,11 @@
         <v>182</v>
       </c>
       <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-    </row>
-    <row r="24" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
+      <c r="F23" s="13" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A24" s="5" t="s">
         <v>168</v>
       </c>
@@ -2550,9 +2515,11 @@
         <v>182</v>
       </c>
       <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="25" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
+      <c r="F24" s="5" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A25" s="5" t="s">
         <v>169</v>
       </c>
@@ -2566,16 +2533,19 @@
         <v>182</v>
       </c>
       <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
+      <c r="F25" s="5" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F25">
-    <filterColumn colId="2">
+    <filterColumn colId="2"/>
+    <filterColumn colId="3">
       <filters>
-        <filter val="刘晓璇"/>
+        <filter val="赵育"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -3762,40 +3732,40 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="409.5" customHeight="1">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
     </row>
     <row r="3" spans="1:14" ht="381" customHeight="1">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="8" t="s">

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="288">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -762,10 +762,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>赵小妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>黄晓妮</t>
   </si>
   <si>
@@ -1169,6 +1165,18 @@
   </si>
   <si>
     <t>与用例14372重复，对应手工用例及自动化用例需删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘晓璇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尹臻/刘晓璇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵小妮/赵育</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2119,7 +2127,7 @@
         <v>174</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>175</v>
@@ -2130,47 +2138,47 @@
         <v>146</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>250</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>251</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="13" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="10" customFormat="1" ht="27">
       <c r="A3" s="5" t="s">
         <v>147</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>178</v>
+        <v>286</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="1:6" s="10" customFormat="1" hidden="1">
+    <row r="4" spans="1:6" s="10" customFormat="1">
       <c r="A4" s="5" t="s">
         <v>148</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>178</v>
+        <v>286</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -2180,17 +2188,17 @@
         <v>149</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>177</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="10" customFormat="1" ht="54" hidden="1">
@@ -2198,17 +2206,17 @@
         <v>150</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>177</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="10" customFormat="1" ht="54" hidden="1">
@@ -2216,167 +2224,167 @@
         <v>151</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>177</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="13" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="10" customFormat="1" ht="27">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
       <c r="A8" s="5" t="s">
         <v>152</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>177</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="13" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="10" customFormat="1" ht="40.5">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="10" customFormat="1" ht="40.5" hidden="1">
       <c r="A9" s="5" t="s">
         <v>153</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>177</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="13" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="10" customFormat="1" ht="40.5">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="10" customFormat="1" ht="40.5" hidden="1">
       <c r="A10" s="5" t="s">
         <v>154</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>177</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="13" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="10" customFormat="1" ht="27">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
       <c r="A11" s="5" t="s">
         <v>155</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>177</v>
+        <v>285</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="13" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="10" customFormat="1" ht="27">
       <c r="A12" s="5" t="s">
         <v>156</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>179</v>
+        <v>287</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
+    <row r="13" spans="1:6" s="10" customFormat="1" ht="27">
       <c r="A13" s="5" t="s">
         <v>157</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>179</v>
+        <v>287</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
     </row>
-    <row r="14" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
+    <row r="14" spans="1:6" s="10" customFormat="1" ht="27">
       <c r="A14" s="5" t="s">
         <v>158</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>178</v>
+        <v>286</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
     </row>
-    <row r="15" spans="1:6" s="10" customFormat="1" hidden="1">
+    <row r="15" spans="1:6" s="10" customFormat="1">
       <c r="A15" s="5" t="s">
         <v>159</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>178</v>
+        <v>286</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
     </row>
-    <row r="16" spans="1:6" s="10" customFormat="1" hidden="1">
+    <row r="16" spans="1:6" s="10" customFormat="1">
       <c r="A16" s="5" t="s">
         <v>160</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>178</v>
+        <v>286</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
@@ -2386,17 +2394,17 @@
         <v>161</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>177</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="10" customFormat="1" ht="40.5" hidden="1">
@@ -2404,17 +2412,17 @@
         <v>162</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>177</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
@@ -2422,13 +2430,13 @@
         <v>163</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>177</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="13"/>
@@ -2438,13 +2446,13 @@
         <v>164</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>177</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="13"/>
@@ -2454,18 +2462,18 @@
         <v>165</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>177</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="13"/>
     </row>
-    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="22" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
       <c r="A22" s="5" t="s">
         <v>166</v>
       </c>
@@ -2473,17 +2481,17 @@
         <v>170</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>178</v>
+        <v>286</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="13" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
       <c r="A23" s="5" t="s">
         <v>167</v>
       </c>
@@ -2491,17 +2499,17 @@
         <v>171</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>178</v>
+        <v>286</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="13" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
       <c r="A24" s="5" t="s">
         <v>168</v>
       </c>
@@ -2509,17 +2517,17 @@
         <v>172</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>178</v>
+        <v>286</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
       <c r="A25" s="5" t="s">
         <v>169</v>
       </c>
@@ -2527,14 +2535,14 @@
         <v>173</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>178</v>
+        <v>286</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2542,10 +2550,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F25">
-    <filterColumn colId="2"/>
-    <filterColumn colId="3">
+    <filterColumn colId="2">
       <filters>
-        <filter val="赵育"/>
+        <filter val="尹臻"/>
+        <filter val="赵小妮"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2589,7 +2597,7 @@
         <v>174</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>175</v>
@@ -2600,7 +2608,7 @@
     </row>
     <row r="2" spans="1:9" hidden="1">
       <c r="A2" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2609,7 +2617,7 @@
         <v>178</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -2617,121 +2625,121 @@
     </row>
     <row r="3" spans="1:9" hidden="1">
       <c r="A3" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>178</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:9" hidden="1">
       <c r="A4" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>178</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:9" hidden="1">
       <c r="A5" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>178</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:9" hidden="1">
       <c r="A6" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>178</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:9" hidden="1">
       <c r="A7" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>178</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:9" hidden="1">
       <c r="A8" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>178</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:9" hidden="1">
       <c r="A9" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>178</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:9" hidden="1">
       <c r="A10" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>178</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="27" hidden="1">
@@ -2742,7 +2750,7 @@
         <v>178</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>141</v>
@@ -2750,563 +2758,563 @@
     </row>
     <row r="14" spans="1:9" hidden="1">
       <c r="A14" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>178</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>178</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>178</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>178</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>178</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>178</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:6" hidden="1">
       <c r="A20" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:6" hidden="1">
       <c r="A21" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:6" hidden="1">
       <c r="A22" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:6" hidden="1">
       <c r="A23" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:6" hidden="1">
       <c r="A29" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:6" hidden="1">
       <c r="A30" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:6" hidden="1">
       <c r="A37" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="1:6" hidden="1">
       <c r="A38" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="39" spans="1:6" hidden="1">
       <c r="A39" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="40" spans="1:6" hidden="1">
       <c r="A40" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:6" hidden="1">
       <c r="A41" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="42" spans="1:6" hidden="1">
       <c r="A42" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="43" spans="1:6" hidden="1">
       <c r="A43" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="1:6" hidden="1">
       <c r="A44" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:6" hidden="1">
       <c r="A45" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46" spans="1:6" hidden="1">
       <c r="A46" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:6" hidden="1">
       <c r="A47" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="48" spans="1:6" hidden="1">
       <c r="A48" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="49" spans="1:6" hidden="1">
       <c r="A49" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="50" spans="1:6" hidden="1">
       <c r="A50" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="51" spans="1:6" hidden="1">
       <c r="A51" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52" spans="1:6" hidden="1">
       <c r="A52" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" spans="1:6" hidden="1">
       <c r="A53" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="54" spans="1:6" hidden="1">
       <c r="A54" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="55" spans="1:6" hidden="1">
       <c r="A55" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="56" spans="1:6" hidden="1">
       <c r="A56" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="59" spans="1:6" hidden="1">
       <c r="A59" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="60" spans="1:6" hidden="1">
       <c r="A60" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:6" hidden="1">
       <c r="A63" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="64" spans="1:6" hidden="1">
       <c r="A64" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="290">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -718,10 +718,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>seqDB-17980</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>seqDB-18260</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1107,14 +1103,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、判断组个数统一用CommLib.OneGroupMode
-2、1个组上多个子表的场景没有覆盖到
-3、插入数据和创建索引测试点有些乱，见用例批注
-4、插入数据建议改为使用公共方法FullTextDBUtils.insertData
-5、不需要先删除所有子表再删主表，删除主表会同时删除主表下挂载的子表（主子表公共问题）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、test里面包含一大堆准备工作的步骤（挂载子表、创建/获取全文索引），实际测试点是插入/更新/删除记录，准备工作建议放到setUp（很多用例都要类似这种问题，请排查修改）
 2、检查结果不完整，如删除没有检查数据不存在、更新没有检查数据是否已被更新正确、插入没有检查插入的数据存在且正确</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1160,14 +1148,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>与用例11981重复，对应手工用例及自动化用例需删除</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>与用例14372重复，对应手工用例及自动化用例需删除</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>刘晓璇</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1177,6 +1157,35 @@
   </si>
   <si>
     <t>赵小妮/赵育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手工用例已调整，请根据手工用例修改自动化用例(赵育)
+1、判断组个数统一用CommLib.OneGroupMode
+2、1个组上多个子表的场景没有覆盖到
+3、插入数据和创建索引测试点有些乱，见用例批注
+4、插入数据建议改为使用公共方法FullTextDBUtils.insertData
+5、不需要先删除所有子表再删主表，删除主表会同时删除主表下挂载的子表（主子表公共问题）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.全文索引正常同步的流程，也可能存在索引删除重建的(比如pop固定集合超时)，后面需要优化数据同步的公共方法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17980</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与用例11981重复，对应手工用例及自动化用例需删除(已删除)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与用例14372重复，对应手工用例及自动化用例需删除(已删除)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1269,7 +1278,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1295,6 +1304,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2121,270 +2131,270 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="10" customFormat="1" ht="36.75" hidden="1" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="13" t="s">
-        <v>252</v>
+      <c r="B2" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>250</v>
-      </c>
       <c r="E2" s="5"/>
-      <c r="F2" s="13" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="10" customFormat="1" ht="27">
+      <c r="F2" s="14" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
       <c r="A3" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>253</v>
+      <c r="B3" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row r="4" spans="1:6" s="10" customFormat="1">
+    <row r="4" spans="1:6" s="10" customFormat="1" hidden="1">
       <c r="A4" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>254</v>
+      <c r="B4" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="1:6" s="10" customFormat="1" ht="67.5" hidden="1">
+    <row r="5" spans="1:6" s="10" customFormat="1" ht="81" hidden="1">
       <c r="A5" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>255</v>
+      <c r="B5" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="13" t="s">
-        <v>274</v>
+      <c r="F5" s="14" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="10" customFormat="1" ht="54" hidden="1">
       <c r="A6" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>256</v>
+      <c r="B6" s="14" t="s">
+        <v>255</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="13" t="s">
-        <v>272</v>
+      <c r="F6" s="14" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="10" customFormat="1" ht="54" hidden="1">
       <c r="A7" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>257</v>
+      <c r="B7" s="14" t="s">
+        <v>256</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="13" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
+      <c r="F7" s="14" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="10" customFormat="1" ht="27">
       <c r="A8" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>258</v>
+      <c r="B8" s="14" t="s">
+        <v>257</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="13" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="10" customFormat="1" ht="40.5" hidden="1">
+      <c r="F8" s="14" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="10" customFormat="1" ht="40.5">
       <c r="A9" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>259</v>
+      <c r="B9" s="14" t="s">
+        <v>258</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="13" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="10" customFormat="1" ht="40.5" hidden="1">
+      <c r="F9" s="14" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="10" customFormat="1" ht="40.5">
       <c r="A10" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>260</v>
+      <c r="B10" s="14" t="s">
+        <v>259</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="13" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
+      <c r="F10" s="14" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="10" customFormat="1" ht="27">
       <c r="A11" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>261</v>
+      <c r="B11" s="14" t="s">
+        <v>260</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="13" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="10" customFormat="1" ht="27">
+      <c r="F11" s="14" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
       <c r="A12" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>262</v>
+      <c r="B12" s="14" t="s">
+        <v>261</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:6" s="10" customFormat="1" ht="27">
+    <row r="13" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
       <c r="A13" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>263</v>
+      <c r="B13" s="14" t="s">
+        <v>262</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
     </row>
-    <row r="14" spans="1:6" s="10" customFormat="1" ht="27">
+    <row r="14" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
       <c r="A14" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>264</v>
+      <c r="B14" s="14" t="s">
+        <v>263</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
     </row>
-    <row r="15" spans="1:6" s="10" customFormat="1">
+    <row r="15" spans="1:6" s="10" customFormat="1" hidden="1">
       <c r="A15" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>265</v>
+      <c r="B15" s="14" t="s">
+        <v>264</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
     </row>
-    <row r="16" spans="1:6" s="10" customFormat="1">
+    <row r="16" spans="1:6" s="10" customFormat="1" hidden="1">
       <c r="A16" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B16" s="13" t="s">
-        <v>266</v>
+      <c r="B16" s="14" t="s">
+        <v>265</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
@@ -2393,156 +2403,160 @@
       <c r="A17" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B17" s="13" t="s">
-        <v>267</v>
+      <c r="B17" s="14" t="s">
+        <v>266</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E17" s="5"/>
-      <c r="F17" s="13" t="s">
-        <v>276</v>
+      <c r="F17" s="14" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="10" customFormat="1" ht="40.5" hidden="1">
       <c r="A18" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B18" s="13" t="s">
-        <v>268</v>
+      <c r="B18" s="14" t="s">
+        <v>267</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E18" s="5"/>
-      <c r="F18" s="13" t="s">
-        <v>277</v>
+      <c r="F18" s="14" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
       <c r="A19" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>269</v>
+      <c r="B19" s="14" t="s">
+        <v>268</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E19" s="5"/>
-      <c r="F19" s="13"/>
+      <c r="F19" s="14"/>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" hidden="1">
       <c r="A20" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B20" s="13" t="s">
-        <v>270</v>
+      <c r="B20" s="14" t="s">
+        <v>269</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E20" s="5"/>
-      <c r="F20" s="13"/>
+      <c r="F20" s="14"/>
     </row>
     <row r="21" spans="1:6" s="10" customFormat="1" hidden="1">
       <c r="A21" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>271</v>
+      <c r="B21" s="14" t="s">
+        <v>270</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="F21" s="13"/>
-    </row>
-    <row r="22" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
+      <c r="F21" s="14"/>
+    </row>
+    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="5" t="s">
         <v>166</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E22" s="5"/>
-      <c r="F22" s="13" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
+      <c r="F22" s="14" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A23" s="5" t="s">
         <v>167</v>
       </c>
       <c r="B23" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="14" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A24" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="13" t="s">
+      <c r="C24" s="5" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
-      <c r="A24" s="5" t="s">
+      <c r="D24" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="A25" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B25" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="20.100000000000001" hidden="1" customHeight="1">
-      <c r="A25" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>173</v>
-      </c>
       <c r="C25" s="5" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E25" s="5"/>
+        <v>180</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>287</v>
+      </c>
       <c r="F25" s="5" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2550,10 +2564,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F25">
-    <filterColumn colId="2">
+    <filterColumn colId="2"/>
+    <filterColumn colId="3">
       <filters>
-        <filter val="尹臻"/>
-        <filter val="赵小妮"/>
+        <filter val="赵育"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2591,16 +2605,16 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>3</v>
@@ -2608,16 +2622,16 @@
     </row>
     <row r="2" spans="1:9" hidden="1">
       <c r="A2" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -2625,121 +2639,121 @@
     </row>
     <row r="3" spans="1:9" hidden="1">
       <c r="A3" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:9" hidden="1">
       <c r="A4" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:9" hidden="1">
       <c r="A5" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:9" hidden="1">
       <c r="A6" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:9" hidden="1">
       <c r="A7" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:9" hidden="1">
       <c r="A8" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:9" hidden="1">
       <c r="A9" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:9" hidden="1">
       <c r="A10" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I10" s="8" t="s">
         <v>247</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="27" hidden="1">
@@ -2747,10 +2761,10 @@
         <v>140</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>141</v>
@@ -2758,563 +2772,563 @@
     </row>
     <row r="14" spans="1:9" hidden="1">
       <c r="A14" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:6" hidden="1">
       <c r="A20" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:6" hidden="1">
       <c r="A21" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:6" hidden="1">
       <c r="A22" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:6" hidden="1">
       <c r="A23" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:6" hidden="1">
       <c r="A29" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:6" hidden="1">
       <c r="A30" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37" spans="1:6" hidden="1">
       <c r="A37" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="38" spans="1:6" hidden="1">
       <c r="A38" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39" spans="1:6" hidden="1">
       <c r="A39" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40" spans="1:6" hidden="1">
       <c r="A40" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41" spans="1:6" hidden="1">
       <c r="A41" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42" spans="1:6" hidden="1">
       <c r="A42" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="1:6" hidden="1">
       <c r="A43" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:6" hidden="1">
       <c r="A44" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="45" spans="1:6" hidden="1">
       <c r="A45" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="46" spans="1:6" hidden="1">
       <c r="A46" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="47" spans="1:6" hidden="1">
       <c r="A47" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="48" spans="1:6" hidden="1">
       <c r="A48" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="49" spans="1:6" hidden="1">
       <c r="A49" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50" spans="1:6" hidden="1">
       <c r="A50" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="51" spans="1:6" hidden="1">
       <c r="A51" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="52" spans="1:6" hidden="1">
       <c r="A52" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="53" spans="1:6" hidden="1">
       <c r="A53" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="54" spans="1:6" hidden="1">
       <c r="A54" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="55" spans="1:6" hidden="1">
       <c r="A55" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="56" spans="1:6" hidden="1">
       <c r="A56" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="59" spans="1:6" hidden="1">
       <c r="A59" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="60" spans="1:6" hidden="1">
       <c r="A60" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="63" spans="1:6" hidden="1">
       <c r="A63" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="64" spans="1:6" hidden="1">
       <c r="A64" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -3728,10 +3742,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="84.5" customWidth="1"/>
+    <col min="1" max="1" width="105" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22.5" customHeight="1">
@@ -3740,49 +3754,54 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="409.5" customHeight="1">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
     </row>
     <row r="3" spans="1:14" ht="381" customHeight="1">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="8" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="8" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="8" t="s">
+    <row r="12" spans="1:14">
+      <c r="A12" s="8" t="s">
         <v>143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="13" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="295">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -632,112 +632,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>seqDB-11981</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-11988</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-11989</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-11990</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-11995</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12015</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12016</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12017</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12018</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12019</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12020</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12065</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12066</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-14372</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-14374</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-14376</t>
-  </si>
-  <si>
-    <t>seqDB-14377</t>
-  </si>
-  <si>
-    <t>seqDB-14397</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-14398</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-14885</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15799</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-18260</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>正在查询固定集合时删除全文索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主表执行truncate清空记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全量同步时，删除原始集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增量同步时，删除原始集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>检视责任人</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -750,264 +644,252 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>尹臻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卢伟康</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检视是否完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12116</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12117</t>
+  </si>
+  <si>
+    <t>seqDB-12120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12121</t>
+  </si>
+  <si>
+    <t>seqDB-12124</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12128</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14414</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14415</t>
+  </si>
+  <si>
+    <t>seqDB-15579</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15796</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15797</t>
+  </si>
+  <si>
+    <t>seqDB-15825</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15826</t>
+  </si>
+  <si>
+    <t>seqDB-15830</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15831</t>
+  </si>
+  <si>
+    <t>seqDB-15832</t>
+  </si>
+  <si>
+    <t>seqDB-15833</t>
+  </si>
+  <si>
+    <t>seqDB-15834</t>
+  </si>
+  <si>
+    <t>seqDB-15835</t>
+  </si>
+  <si>
+    <t>seqDB-15836</t>
+  </si>
+  <si>
+    <t>seqDB-15837</t>
+  </si>
+  <si>
+    <t>seqDB-15838</t>
+  </si>
+  <si>
+    <t>seqDB-15839</t>
+  </si>
+  <si>
+    <t>seqDB-15840</t>
+  </si>
+  <si>
+    <t>seqDB-15841</t>
+  </si>
+  <si>
+    <t>seqDB-15842</t>
+  </si>
+  <si>
+    <t>seqDB-15843</t>
+  </si>
+  <si>
+    <t>seqDB-15844</t>
+  </si>
+  <si>
+    <t>seqDB-15845</t>
+  </si>
+  <si>
+    <t>seqDB-15846</t>
+  </si>
+  <si>
+    <t>seqDB-15847</t>
+  </si>
+  <si>
+    <t>seqDB-15848</t>
+  </si>
+  <si>
+    <t>seqDB-15849</t>
+  </si>
+  <si>
+    <t>seqDB-15850</t>
+  </si>
+  <si>
+    <t>seqDB-15851</t>
+  </si>
+  <si>
+    <t>seqDB-15852</t>
+  </si>
+  <si>
+    <t>seqDB-15853</t>
+  </si>
+  <si>
+    <t>seqDB-15854</t>
+  </si>
+  <si>
+    <t>seqDB-15855</t>
+  </si>
+  <si>
+    <t>seqDB-15856</t>
+  </si>
+  <si>
+    <t>seqDB-15857</t>
+  </si>
+  <si>
+    <t>seqDB-15858</t>
+  </si>
+  <si>
+    <t>seqDB-15859</t>
+  </si>
+  <si>
+    <t>seqDB-15860</t>
+  </si>
+  <si>
+    <t>seqDB-15874</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15875</t>
+  </si>
+  <si>
+    <t>seqDB-15876</t>
+  </si>
+  <si>
+    <t>seqDB-15877</t>
+  </si>
+  <si>
+    <t>seqDB-15879</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15880</t>
+  </si>
+  <si>
+    <t>seqDB-15881</t>
+  </si>
+  <si>
+    <t>seqDB-18259</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12118</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12125</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12126</t>
+  </si>
+  <si>
+    <t>seqDB-12127</t>
+  </si>
+  <si>
+    <t>seqDB-12129</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12119</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12122</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15871</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15872</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘晓旋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据量大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>刘晓璇</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>尹臻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>黄晓妮</t>
-  </si>
-  <si>
-    <t>黄晓妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>赵育</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>卢伟康</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检视是否完成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12116</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12117</t>
-  </si>
-  <si>
-    <t>seqDB-12120</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12121</t>
-  </si>
-  <si>
-    <t>seqDB-12124</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12128</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-14414</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-14415</t>
-  </si>
-  <si>
-    <t>seqDB-15579</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15796</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15797</t>
-  </si>
-  <si>
-    <t>seqDB-15825</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15826</t>
-  </si>
-  <si>
-    <t>seqDB-15830</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15831</t>
-  </si>
-  <si>
-    <t>seqDB-15832</t>
-  </si>
-  <si>
-    <t>seqDB-15833</t>
-  </si>
-  <si>
-    <t>seqDB-15834</t>
-  </si>
-  <si>
-    <t>seqDB-15835</t>
-  </si>
-  <si>
-    <t>seqDB-15836</t>
-  </si>
-  <si>
-    <t>seqDB-15837</t>
-  </si>
-  <si>
-    <t>seqDB-15838</t>
-  </si>
-  <si>
-    <t>seqDB-15839</t>
-  </si>
-  <si>
-    <t>seqDB-15840</t>
-  </si>
-  <si>
-    <t>seqDB-15841</t>
-  </si>
-  <si>
-    <t>seqDB-15842</t>
-  </si>
-  <si>
-    <t>seqDB-15843</t>
-  </si>
-  <si>
-    <t>seqDB-15844</t>
-  </si>
-  <si>
-    <t>seqDB-15845</t>
-  </si>
-  <si>
-    <t>seqDB-15846</t>
-  </si>
-  <si>
-    <t>seqDB-15847</t>
-  </si>
-  <si>
-    <t>seqDB-15848</t>
-  </si>
-  <si>
-    <t>seqDB-15849</t>
-  </si>
-  <si>
-    <t>seqDB-15850</t>
-  </si>
-  <si>
-    <t>seqDB-15851</t>
-  </si>
-  <si>
-    <t>seqDB-15852</t>
-  </si>
-  <si>
-    <t>seqDB-15853</t>
-  </si>
-  <si>
-    <t>seqDB-15854</t>
-  </si>
-  <si>
-    <t>seqDB-15855</t>
-  </si>
-  <si>
-    <t>seqDB-15856</t>
-  </si>
-  <si>
-    <t>seqDB-15857</t>
-  </si>
-  <si>
-    <t>seqDB-15858</t>
-  </si>
-  <si>
-    <t>seqDB-15859</t>
-  </si>
-  <si>
-    <t>seqDB-15860</t>
-  </si>
-  <si>
-    <t>seqDB-15874</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15875</t>
-  </si>
-  <si>
-    <t>seqDB-15876</t>
-  </si>
-  <si>
-    <t>seqDB-15877</t>
-  </si>
-  <si>
-    <t>seqDB-15879</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15880</t>
-  </si>
-  <si>
-    <t>seqDB-15881</t>
-  </si>
-  <si>
-    <t>seqDB-18259</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12123</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12118</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12125</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12126</t>
-  </si>
-  <si>
-    <t>seqDB-12127</t>
-  </si>
-  <si>
-    <t>seqDB-12129</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12119</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12122</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15871</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15872</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘晓旋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据量大</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘晓璇</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄晓妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄晓妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在非空集合中创建/删除全文索引</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1090,6 +972,66 @@
     <t>1、文本用例和自动化用例检查点不完整，缺少：固定集合与原集合数据一致性检查、节点间数据一致性检查。
 2、test中的db.close建议在try里面新建连接，如果多个步骤使用建议放到finally关闭
 3、存在db连接未关闭告警</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、test里面包含一大堆准备工作的步骤（挂载子表、创建/获取全文索引），实际测试点是插入/更新/删除记录，准备工作建议放到setUp（很多用例都要类似这种问题，请排查修改）
+2、检查结果不完整，如删除没有检查数据不存在、更新没有检查数据是否已被更新正确、插入没有检查插入的数据存在且正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.切分表需要分组校验数据量，统一新增公共方法进行校验
+2.teardown里面统一校验下固定集合是否残留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.切分表需要分组校验数据量，统一新增公共方法进行校验
+2.注释部分文件名为手工用例编号及标题
+3.teardown里面统一校验下固定集合是否残留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.定义的集合名字需修改成规范的
+2.删除全文索引的时候需要规避-190，避免用例随机失败
+3.删除全文索引后，需要检查固定集合主备节点均无残留,遗漏检测点
+4.上下文无残留，需要确认下是否可以校验；
+5.teardown里面统一校验下固定集合、ES是否残留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵小妮/赵育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.全文索引正常同步的流程，也可能存在索引删除重建的(比如pop固定集合超时)，后面需要优化数据同步的公共方法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-17980</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与用例14372重复，对应手工用例及自动化用例需删除(已删除)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-11981</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在非空集合中创建/删除全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘晓璇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1103,52 +1045,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、test里面包含一大堆准备工作的步骤（挂载子表、创建/获取全文索引），实际测试点是插入/更新/删除记录，准备工作建议放到setUp（很多用例都要类似这种问题，请排查修改）
-2、检查结果不完整，如删除没有检查数据不存在、更新没有检查数据是否已被更新正确、插入没有检查插入的数据存在且正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、代码逻辑不够清晰，建议优化，见用例批注
-2、很多db.close不规范的哦（公共问题）
-3、检查结果同12015</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、代码貌似跟 14374 没区别（一个时es没数据，一个时数据处理中，但是代码层面看不出区别，且测试点怎么保证有测到点上？）
-2、其他同14374</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.切分表需要分组校验数据量，统一新增公共方法进行校验
-2.teardown里面统一校验下固定集合是否残留</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.切分表需要分组校验数据量，统一新增公共方法进行校验
-2.注释部分文件名为手工用例编号及标题
-3.teardown里面统一校验下固定集合是否残留</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.truncate集合的时候，需要修改调用修改后的公共方法
-2.teardown里面统一校验下固定集合、ES是否残留</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.定义的集合名字需修改成规范的
-2.删除全文索引的时候需要规避-190，避免用例随机失败
-3.删除全文索引后，需要检查固定集合主备节点均无残留,遗漏检测点
-4.上下文无残留，需要确认下是否可以校验；
-5.teardown里面统一校验下固定集合、ES是否残留</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.truncate集合的时候，需要修改调用修改后的公共方法
-2.teardown里面统一校验下固定集合、ES是否残留</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘晓璇</t>
+    <t>seqDB-11988</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1156,7 +1053,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>赵小妮/赵育</t>
+    <t>seqDB-11989</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-11990</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1169,15 +1070,126 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3.全文索引正常同步的流程，也可能存在索引删除重建的(比如pop固定集合超时)，后面需要优化数据同步的公共方法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-17980</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
+    <t>seqDB-11995</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卢伟康</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12018</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12019</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.truncate集合的时候，需要修改调用修改后的公共方法
+2.teardown里面统一校验下固定集合、ES是否残留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、判断组个数统一用CommLib.OneGroupMode
+2、插入数据无特殊场景考虑，建议使用公共方法
+3、teardown删除cl需要使用公共方法，另外关闭sdb和es连接需要放到finally
+4、teardown需要添加固定集合是否残留的检查（赵育新加的规范：所有用例teardown都需要检查固定集合和索引是否有残留）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同 12020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12065</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12066</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14372</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14374</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、代码逻辑不够清晰，建议优化，见用例批注
+2、很多db.close不规范的哦（公共问题）
+3、检查结果同12015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14376</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、代码貌似跟 14374 没区别（一个时es没数据，一个时数据处理中，但是代码层面看不出区别，且测试点怎么保证有测到点上？）
+2、其他同14374</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14377</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14397</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同 11981，测试点有些乱，需要重新梳理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14398</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14885</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正在查询固定集合时删除全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15799</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主表执行truncate清空记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全量同步时，删除原始集合</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1185,7 +1197,21 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>与用例14372重复，对应手工用例及自动化用例需删除(已删除)</t>
+    <t>seqDB-18260</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增量同步时，删除原始集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、文本用例测的是“加入域”并自动切分，自动化用例没有域和自动切分，测试点没测到
+2、其他问题同 seqDB-11981</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、测试点不清晰，见用例注释
+2、删除索引没有校验节点间数据一致性</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1278,7 +1304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1299,15 +1325,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1318,6 +1343,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1329,7 +1422,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -2111,15 +2204,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.375" customWidth="1"/>
     <col min="2" max="2" width="33.875" customWidth="1"/>
-    <col min="3" max="3" width="20.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="33.375" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="3" max="3" width="14.125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="11.75" customWidth="1"/>
+    <col min="5" max="5" width="10.5" customWidth="1"/>
     <col min="6" max="6" width="84.625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2131,432 +2223,444 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>182</v>
+        <v>146</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>154</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="10" customFormat="1" ht="36.75" hidden="1" customHeight="1">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="13" customFormat="1" ht="148.5">
       <c r="A2" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="B2" s="14" t="s">
         <v>251</v>
       </c>
+      <c r="B2" s="12" t="s">
+        <v>252</v>
+      </c>
       <c r="C2" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="13" customFormat="1" ht="27">
+      <c r="A3" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="12" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="13" customFormat="1" ht="27">
+      <c r="A4" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="13" customFormat="1" ht="81">
+      <c r="A5" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="13" customFormat="1" ht="54">
+      <c r="A6" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="13" customFormat="1" ht="54">
+      <c r="A7" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="12" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="13" customFormat="1" ht="27">
+      <c r="A8" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="12" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="13" customFormat="1" ht="40.5">
+      <c r="A9" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="13" customFormat="1" ht="40.5">
+      <c r="A10" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="13" customFormat="1" ht="27">
+      <c r="A11" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="13" customFormat="1" ht="67.5">
+      <c r="A12" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="12" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="13" customFormat="1" ht="27">
+      <c r="A13" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="12" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="13" customFormat="1" ht="27">
+      <c r="A14" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="12"/>
+    </row>
+    <row r="15" spans="1:6" s="13" customFormat="1">
+      <c r="A15" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="12"/>
+    </row>
+    <row r="16" spans="1:6" s="13" customFormat="1">
+      <c r="A16" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="12"/>
+    </row>
+    <row r="17" spans="1:6" s="13" customFormat="1" ht="40.5">
+      <c r="A17" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="12" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="13" customFormat="1" ht="40.5">
+      <c r="A18" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="12" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="13" customFormat="1" ht="27">
+      <c r="A19" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="12"/>
+    </row>
+    <row r="20" spans="1:6" s="13" customFormat="1">
+      <c r="A20" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="12" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="13" customFormat="1">
+      <c r="A21" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="12" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="13" customFormat="1" ht="67.5">
+      <c r="A22" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="12" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="13" customFormat="1" ht="27">
+      <c r="A23" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" s="13" customFormat="1">
+      <c r="A24" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="B24" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="14" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
-      <c r="A3" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-    </row>
-    <row r="4" spans="1:6" s="10" customFormat="1" hidden="1">
-      <c r="A4" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-    </row>
-    <row r="5" spans="1:6" s="10" customFormat="1" ht="81" hidden="1">
-      <c r="A5" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="14" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="10" customFormat="1" ht="54" hidden="1">
-      <c r="A6" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="14" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="10" customFormat="1" ht="54" hidden="1">
-      <c r="A7" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="14" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="10" customFormat="1" ht="27">
-      <c r="A8" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="B8" s="14" t="s">
+      <c r="F24" s="12" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" s="13" customFormat="1">
+      <c r="A25" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="14" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="10" customFormat="1" ht="40.5">
-      <c r="A9" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="14" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="10" customFormat="1" ht="40.5">
-      <c r="A10" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="14" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="10" customFormat="1" ht="27">
-      <c r="A11" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="14" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
-      <c r="A12" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
-      <c r="A13" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="D13" s="5" t="s">
+      <c r="D25" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="F25" s="12" t="s">
         <v>250</v>
-      </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
-      <c r="A14" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:6" s="10" customFormat="1" hidden="1">
-      <c r="A15" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" spans="1:6" s="10" customFormat="1" hidden="1">
-      <c r="A16" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="17" spans="1:6" s="10" customFormat="1" ht="40.5" hidden="1">
-      <c r="A17" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="14" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="10" customFormat="1" ht="40.5" hidden="1">
-      <c r="A18" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="14" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="10" customFormat="1" ht="27" hidden="1">
-      <c r="A19" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="14"/>
-    </row>
-    <row r="20" spans="1:6" s="10" customFormat="1" hidden="1">
-      <c r="A20" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="14"/>
-    </row>
-    <row r="21" spans="1:6" s="10" customFormat="1" hidden="1">
-      <c r="A21" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="14"/>
-    </row>
-    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="14" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="14" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2565,11 +2669,7 @@
   </sheetData>
   <autoFilter ref="A1:F25">
     <filterColumn colId="2"/>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="赵育"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="3"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2605,16 +2705,16 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>182</v>
+        <v>146</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>154</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>3</v>
@@ -2622,16 +2722,16 @@
     </row>
     <row r="2" spans="1:9" hidden="1">
       <c r="A2" s="8" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="8" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -2639,121 +2739,121 @@
     </row>
     <row r="3" spans="1:9" hidden="1">
       <c r="A3" s="8" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:9" hidden="1">
       <c r="A4" s="8" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:9" hidden="1">
       <c r="A5" s="8" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:9" hidden="1">
       <c r="A6" s="8" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:9" hidden="1">
       <c r="A7" s="8" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:9" hidden="1">
       <c r="A8" s="8" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:9" hidden="1">
       <c r="A9" s="8" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:9" hidden="1">
       <c r="A10" s="8" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>247</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="8" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="8" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="27" hidden="1">
@@ -2761,10 +2861,10 @@
         <v>140</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>141</v>
@@ -2772,563 +2872,563 @@
     </row>
     <row r="14" spans="1:9" hidden="1">
       <c r="A14" s="8" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="8" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="8" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="8" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="8" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="8" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:6" hidden="1">
       <c r="A20" s="8" t="s">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:6" hidden="1">
       <c r="A21" s="8" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:6" hidden="1">
       <c r="A22" s="8" t="s">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:6" hidden="1">
       <c r="A23" s="8" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="8" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="8" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="8" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="8" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="8" t="s">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:6" hidden="1">
       <c r="A29" s="8" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" spans="1:6" hidden="1">
       <c r="A30" s="8" t="s">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="8" t="s">
-        <v>211</v>
+        <v>183</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="8" t="s">
-        <v>212</v>
+        <v>184</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="8" t="s">
-        <v>213</v>
+        <v>185</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="8" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="8" t="s">
-        <v>215</v>
+        <v>187</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="8" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:6" hidden="1">
       <c r="A37" s="8" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:6" hidden="1">
       <c r="A38" s="8" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:6" hidden="1">
       <c r="A39" s="8" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40" spans="1:6" hidden="1">
       <c r="A40" s="8" t="s">
-        <v>220</v>
+        <v>192</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:6" hidden="1">
       <c r="A41" s="8" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:6" hidden="1">
       <c r="A42" s="8" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:6" hidden="1">
       <c r="A43" s="8" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="44" spans="1:6" hidden="1">
       <c r="A44" s="8" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="45" spans="1:6" hidden="1">
       <c r="A45" s="8" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="46" spans="1:6" hidden="1">
       <c r="A46" s="8" t="s">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="47" spans="1:6" hidden="1">
       <c r="A47" s="8" t="s">
-        <v>227</v>
+        <v>199</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48" spans="1:6" hidden="1">
       <c r="A48" s="8" t="s">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
     <row r="49" spans="1:6" hidden="1">
       <c r="A49" s="8" t="s">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="50" spans="1:6" hidden="1">
       <c r="A50" s="8" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="51" spans="1:6" hidden="1">
       <c r="A51" s="8" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:6" hidden="1">
       <c r="A52" s="8" t="s">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53" spans="1:6" hidden="1">
       <c r="A53" s="8" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="54" spans="1:6" hidden="1">
       <c r="A54" s="8" t="s">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="55" spans="1:6" hidden="1">
       <c r="A55" s="8" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" spans="1:6" hidden="1">
       <c r="A56" s="8" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="8" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="8" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="59" spans="1:6" hidden="1">
       <c r="A59" s="8" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="1:6" hidden="1">
       <c r="A60" s="8" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="8" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="8" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="63" spans="1:6" hidden="1">
       <c r="A63" s="8" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" spans="1:6" hidden="1">
       <c r="A64" s="8" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -3754,40 +3854,40 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="409.5" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
     </row>
     <row r="3" spans="1:14" ht="381" customHeight="1">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="8" t="s">
@@ -3800,8 +3900,8 @@
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="13" t="s">
-        <v>285</v>
+      <c r="A13" s="11" t="s">
+        <v>247</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="正常功能" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <sheet name="自动化用例问题收集" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">并发功能!$F$1:$F$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">并发功能!$A$1:$I$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">大数据用例!$A$1:$F$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">正常功能!$C$1:$C$25</definedName>
   </definedNames>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="296">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1212,6 +1212,10 @@
   <si>
     <t>1、测试点不清晰，见用例注释
 2、删除索引没有校验节点间数据一致性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已检视，见用例批注</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1304,7 +1308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1332,6 +1336,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2679,7 +2684,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I64"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -2720,7 +2724,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1">
+    <row r="2" spans="1:9">
       <c r="A2" s="8" t="s">
         <v>155</v>
       </c>
@@ -2737,7 +2741,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" hidden="1">
+    <row r="3" spans="1:9">
       <c r="A3" s="8" t="s">
         <v>156</v>
       </c>
@@ -2748,7 +2752,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1">
+    <row r="4" spans="1:9">
       <c r="A4" s="8" t="s">
         <v>157</v>
       </c>
@@ -2759,7 +2763,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1">
+    <row r="5" spans="1:9">
       <c r="A5" s="8" t="s">
         <v>158</v>
       </c>
@@ -2770,7 +2774,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1">
+    <row r="6" spans="1:9">
       <c r="A6" s="8" t="s">
         <v>159</v>
       </c>
@@ -2781,7 +2785,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1">
+    <row r="7" spans="1:9">
       <c r="A7" s="8" t="s">
         <v>160</v>
       </c>
@@ -2792,7 +2796,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1">
+    <row r="8" spans="1:9">
       <c r="A8" s="8" t="s">
         <v>161</v>
       </c>
@@ -2803,7 +2807,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1">
+    <row r="9" spans="1:9">
       <c r="A9" s="8" t="s">
         <v>162</v>
       </c>
@@ -2814,7 +2818,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1">
+    <row r="10" spans="1:9">
       <c r="A10" s="8" t="s">
         <v>163</v>
       </c>
@@ -2844,6 +2848,9 @@
       <c r="F11" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="H11" s="14" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="8" t="s">
@@ -2855,8 +2862,11 @@
       <c r="F12" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="27" hidden="1">
+      <c r="H12" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="27">
       <c r="A13" s="8" t="s">
         <v>140</v>
       </c>
@@ -2870,7 +2880,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1">
+    <row r="14" spans="1:9">
       <c r="A14" s="8" t="s">
         <v>166</v>
       </c>
@@ -2891,6 +2901,9 @@
       <c r="F15" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="H15" s="14" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="8" t="s">
@@ -2902,8 +2915,11 @@
       <c r="F16" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="H16" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="8" t="s">
         <v>169</v>
       </c>
@@ -2913,8 +2929,11 @@
       <c r="F17" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="H17" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="8" t="s">
         <v>170</v>
       </c>
@@ -2924,8 +2943,11 @@
       <c r="F18" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="H18" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="8" t="s">
         <v>171</v>
       </c>
@@ -2935,8 +2957,11 @@
       <c r="F19" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" hidden="1">
+      <c r="H19" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="8" t="s">
         <v>172</v>
       </c>
@@ -2947,7 +2972,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1">
+    <row r="21" spans="1:8">
       <c r="A21" s="8" t="s">
         <v>173</v>
       </c>
@@ -2958,7 +2983,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1">
+    <row r="22" spans="1:8">
       <c r="A22" s="8" t="s">
         <v>174</v>
       </c>
@@ -2969,7 +2994,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1">
+    <row r="23" spans="1:8">
       <c r="A23" s="8" t="s">
         <v>175</v>
       </c>
@@ -2980,7 +3005,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:8">
       <c r="A24" s="8" t="s">
         <v>176</v>
       </c>
@@ -2990,8 +3015,11 @@
       <c r="F24" s="8" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="H24" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="8" t="s">
         <v>177</v>
       </c>
@@ -3001,8 +3029,11 @@
       <c r="F25" s="8" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="H25" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="8" t="s">
         <v>178</v>
       </c>
@@ -3012,8 +3043,11 @@
       <c r="F26" s="8" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="H26" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="8" t="s">
         <v>179</v>
       </c>
@@ -3023,8 +3057,11 @@
       <c r="F27" s="8" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="H27" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="8" t="s">
         <v>180</v>
       </c>
@@ -3034,8 +3071,11 @@
       <c r="F28" s="8" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" hidden="1">
+      <c r="H28" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="8" t="s">
         <v>181</v>
       </c>
@@ -3046,7 +3086,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="30" spans="1:6" hidden="1">
+    <row r="30" spans="1:8">
       <c r="A30" s="8" t="s">
         <v>182</v>
       </c>
@@ -3057,7 +3097,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:8">
       <c r="A31" s="8" t="s">
         <v>183</v>
       </c>
@@ -3067,8 +3107,11 @@
       <c r="F31" s="8" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="H31" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="8" t="s">
         <v>184</v>
       </c>
@@ -3078,8 +3121,11 @@
       <c r="F32" s="8" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="H32" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="8" t="s">
         <v>185</v>
       </c>
@@ -3089,8 +3135,11 @@
       <c r="F33" s="8" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="H33" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="8" t="s">
         <v>186</v>
       </c>
@@ -3100,8 +3149,11 @@
       <c r="F34" s="8" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="H34" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="8" t="s">
         <v>187</v>
       </c>
@@ -3111,8 +3163,11 @@
       <c r="F35" s="8" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="H35" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="8" t="s">
         <v>188</v>
       </c>
@@ -3122,8 +3177,11 @@
       <c r="F36" s="8" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" hidden="1">
+      <c r="H36" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="8" t="s">
         <v>189</v>
       </c>
@@ -3134,7 +3192,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="38" spans="1:6" hidden="1">
+    <row r="38" spans="1:8">
       <c r="A38" s="8" t="s">
         <v>190</v>
       </c>
@@ -3145,7 +3203,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="39" spans="1:6" hidden="1">
+    <row r="39" spans="1:8">
       <c r="A39" s="8" t="s">
         <v>191</v>
       </c>
@@ -3156,7 +3214,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="40" spans="1:6" hidden="1">
+    <row r="40" spans="1:8">
       <c r="A40" s="8" t="s">
         <v>192</v>
       </c>
@@ -3167,7 +3225,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1">
+    <row r="41" spans="1:8">
       <c r="A41" s="8" t="s">
         <v>193</v>
       </c>
@@ -3178,7 +3236,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1">
+    <row r="42" spans="1:8">
       <c r="A42" s="8" t="s">
         <v>194</v>
       </c>
@@ -3189,7 +3247,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1">
+    <row r="43" spans="1:8">
       <c r="A43" s="8" t="s">
         <v>195</v>
       </c>
@@ -3200,7 +3258,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1">
+    <row r="44" spans="1:8">
       <c r="A44" s="8" t="s">
         <v>196</v>
       </c>
@@ -3211,7 +3269,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1">
+    <row r="45" spans="1:8">
       <c r="A45" s="8" t="s">
         <v>197</v>
       </c>
@@ -3222,7 +3280,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1">
+    <row r="46" spans="1:8">
       <c r="A46" s="8" t="s">
         <v>198</v>
       </c>
@@ -3233,7 +3291,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1">
+    <row r="47" spans="1:8">
       <c r="A47" s="8" t="s">
         <v>199</v>
       </c>
@@ -3244,7 +3302,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1">
+    <row r="48" spans="1:8">
       <c r="A48" s="8" t="s">
         <v>200</v>
       </c>
@@ -3255,7 +3313,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1">
+    <row r="49" spans="1:8">
       <c r="A49" s="8" t="s">
         <v>201</v>
       </c>
@@ -3266,7 +3324,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1">
+    <row r="50" spans="1:8">
       <c r="A50" s="8" t="s">
         <v>202</v>
       </c>
@@ -3277,7 +3335,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1">
+    <row r="51" spans="1:8">
       <c r="A51" s="8" t="s">
         <v>203</v>
       </c>
@@ -3288,7 +3346,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1">
+    <row r="52" spans="1:8">
       <c r="A52" s="8" t="s">
         <v>204</v>
       </c>
@@ -3299,7 +3357,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1">
+    <row r="53" spans="1:8">
       <c r="A53" s="8" t="s">
         <v>205</v>
       </c>
@@ -3310,7 +3368,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1">
+    <row r="54" spans="1:8">
       <c r="A54" s="8" t="s">
         <v>206</v>
       </c>
@@ -3321,7 +3379,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1">
+    <row r="55" spans="1:8">
       <c r="A55" s="8" t="s">
         <v>207</v>
       </c>
@@ -3332,7 +3390,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1">
+    <row r="56" spans="1:8">
       <c r="A56" s="8" t="s">
         <v>208</v>
       </c>
@@ -3343,7 +3401,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:8">
       <c r="A57" s="8" t="s">
         <v>209</v>
       </c>
@@ -3353,8 +3411,11 @@
       <c r="F57" s="8" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="58" spans="1:6">
+      <c r="H57" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" s="8" t="s">
         <v>210</v>
       </c>
@@ -3364,8 +3425,11 @@
       <c r="F58" s="8" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" hidden="1">
+      <c r="H58" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59" s="8" t="s">
         <v>211</v>
       </c>
@@ -3376,7 +3440,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1">
+    <row r="60" spans="1:8">
       <c r="A60" s="8" t="s">
         <v>212</v>
       </c>
@@ -3387,7 +3451,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:8">
       <c r="A61" s="8" t="s">
         <v>213</v>
       </c>
@@ -3397,8 +3461,11 @@
       <c r="F61" s="8" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="62" spans="1:6">
+      <c r="H61" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" s="8" t="s">
         <v>214</v>
       </c>
@@ -3408,8 +3475,11 @@
       <c r="F62" s="8" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" hidden="1">
+      <c r="H62" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" s="8" t="s">
         <v>215</v>
       </c>
@@ -3420,7 +3490,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1">
+    <row r="64" spans="1:8">
       <c r="A64" s="8" t="s">
         <v>216</v>
       </c>
@@ -3432,13 +3502,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="F1:F64">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="黄晓妮"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I64"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3854,40 +3918,40 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="409.5" customHeight="1">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
     </row>
     <row r="3" spans="1:14" ht="381" customHeight="1">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="8" t="s">

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="300">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -612,10 +612,6 @@
     <t>seqDB-15798</t>
   </si>
   <si>
-    <t>不连接适配器去执行的这个点无法实现自动化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.数据同步到ES的时间暂时定为1个小时，后面需根据性能测试结果调整该参数为5分钟</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1216,6 +1212,26 @@
   </si>
   <si>
     <t>已检视，见用例批注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检视责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已检视，见用例批注。再次检视完成。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不连接适配器去执行的这个点无法实现自动化</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1308,7 +1324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1337,11 +1353,37 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1735,7 +1777,7 @@
     </row>
     <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
@@ -2179,7 +2221,7 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>139</v>
@@ -2209,6 +2251,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -2228,444 +2271,444 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="13" customFormat="1" ht="148.5">
       <c r="A2" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="C2" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>253</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>254</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="13" customFormat="1" ht="27">
       <c r="A3" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>257</v>
-      </c>
       <c r="D3" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="13" customFormat="1" ht="27">
       <c r="A4" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="13" customFormat="1" ht="81">
       <c r="A5" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>220</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>221</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="12" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="13" customFormat="1" ht="54" hidden="1">
+      <c r="A6" s="5" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" s="13" customFormat="1" ht="54">
-      <c r="A6" s="5" t="s">
+      <c r="B6" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>261</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>262</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="12" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="13" customFormat="1" ht="54">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="13" customFormat="1" ht="54" hidden="1">
       <c r="A7" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="12" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="13" customFormat="1" ht="27">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="13" customFormat="1" ht="27" hidden="1">
       <c r="A8" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>264</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>265</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="12" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="13" customFormat="1" ht="40.5">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="13" customFormat="1" ht="40.5" hidden="1">
       <c r="A9" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="13" customFormat="1" ht="40.5">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="13" customFormat="1" ht="40.5" hidden="1">
       <c r="A10" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="13" customFormat="1" ht="27">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="13" customFormat="1" ht="27" hidden="1">
       <c r="A11" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="13" customFormat="1" ht="67.5">
       <c r="A12" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="13" customFormat="1" ht="27">
       <c r="A13" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="12" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="13" customFormat="1" ht="27" hidden="1">
+      <c r="A14" s="5" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" s="13" customFormat="1" ht="27">
-      <c r="A14" s="5" t="s">
-        <v>274</v>
-      </c>
       <c r="B14" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="12"/>
     </row>
-    <row r="15" spans="1:6" s="13" customFormat="1">
+    <row r="15" spans="1:6" s="13" customFormat="1" hidden="1">
       <c r="A15" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="1:6" s="13" customFormat="1">
+    <row r="16" spans="1:6" s="13" customFormat="1" hidden="1">
       <c r="A16" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="12"/>
     </row>
-    <row r="17" spans="1:6" s="13" customFormat="1" ht="40.5">
+    <row r="17" spans="1:6" s="13" customFormat="1" ht="40.5" hidden="1">
       <c r="A17" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="12" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="13" customFormat="1" ht="40.5" hidden="1">
+      <c r="A18" s="5" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" s="13" customFormat="1" ht="40.5">
-      <c r="A18" s="5" t="s">
-        <v>279</v>
-      </c>
       <c r="B18" s="12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="12" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="13" customFormat="1" ht="27" hidden="1">
+      <c r="A19" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" s="13" customFormat="1" ht="27">
-      <c r="A19" s="5" t="s">
-        <v>281</v>
-      </c>
       <c r="B19" s="12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="12"/>
     </row>
     <row r="20" spans="1:6" s="13" customFormat="1">
       <c r="A20" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C20" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>220</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>221</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:6" s="13" customFormat="1">
       <c r="A21" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>220</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>221</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="12" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" s="13" customFormat="1" ht="67.5">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="13" customFormat="1" ht="67.5" hidden="1">
       <c r="A22" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="B22" s="12" t="s">
-        <v>286</v>
-      </c>
       <c r="C22" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="12" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" s="13" customFormat="1" ht="27">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="13" customFormat="1" ht="27" hidden="1">
       <c r="A23" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="B23" s="12" t="s">
-        <v>288</v>
-      </c>
       <c r="C23" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="12" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" s="13" customFormat="1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" s="13" customFormat="1" hidden="1">
       <c r="A24" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="F24" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E24" s="5" t="s">
+    </row>
+    <row r="25" spans="1:6" s="13" customFormat="1" hidden="1">
+      <c r="A25" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="F25" s="12" t="s">
         <v>249</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" s="13" customFormat="1">
-      <c r="A25" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2674,7 +2717,11 @@
   </sheetData>
   <autoFilter ref="A1:F25">
     <filterColumn colId="2"/>
-    <filterColumn colId="3"/>
+    <filterColumn colId="3">
+      <filters>
+        <filter val="黄晓妮"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2688,818 +2735,1173 @@
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.75" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="15.25" customWidth="1"/>
-    <col min="4" max="4" width="16.5" customWidth="1"/>
-    <col min="5" max="7" width="16.5" style="8" customWidth="1"/>
-    <col min="8" max="9" width="30.625" customWidth="1"/>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="3" max="4" width="8.625" style="17" customWidth="1"/>
+    <col min="5" max="6" width="9.875" style="24" customWidth="1"/>
+    <col min="7" max="7" width="10.125" style="17" customWidth="1"/>
+    <col min="8" max="8" width="37.375" customWidth="1"/>
+    <col min="9" max="9" width="39.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" s="20" customFormat="1" ht="27">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="8" t="s">
+      <c r="F2" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="G2" s="16"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="8" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="G3" s="21"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="G4" s="21"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="G5" s="21"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="G6" s="21"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="G7" s="21"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="G8" s="21"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="G9" s="21"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="G10" s="21"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="G13" s="21"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="G14" s="21"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="G15" s="21"/>
+      <c r="H15" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="G16" s="21"/>
+      <c r="H16" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="G17" s="21"/>
+      <c r="H17" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="G18" s="21"/>
+      <c r="H18" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="G19" s="21"/>
+      <c r="H19" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G20" s="21"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G21" s="21"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G22" s="21"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G23" s="21"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="G24" s="21"/>
+      <c r="H24" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I24" s="5"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="21"/>
+      <c r="H25" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="G26" s="21"/>
+      <c r="H26" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="G27" s="21"/>
+      <c r="H27" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I27" s="5"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="G28" s="21"/>
+      <c r="H28" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I28" s="5"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G29" s="21"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G30" s="21"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="G31" s="21"/>
+      <c r="H31" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I31" s="5"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F32" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="G32" s="21"/>
+      <c r="H32" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I32" s="5"/>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F33" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="G33" s="21"/>
+      <c r="H33" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I33" s="5"/>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F34" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="G34" s="21"/>
+      <c r="H34" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I34" s="5"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F35" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G35" s="21"/>
+      <c r="H35" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I35" s="5"/>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="F36" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G36" s="21"/>
+      <c r="H36" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I36" s="5"/>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B37" s="5"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F37" s="22" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="G37" s="21"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F38" s="22" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G38" s="21"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F39" s="22" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="G39" s="21"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F40" s="22" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="E11" s="8" t="s">
+      <c r="G40" s="21"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F41" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="G41" s="21"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F42" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="G42" s="21"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B43" s="5"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F43" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G43" s="21"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F44" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G44" s="21"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F45" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G45" s="21"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B46" s="5"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F46" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G46" s="21"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F47" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G47" s="21"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F48" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="G48" s="21"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F49" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G49" s="21"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F50" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G50" s="21"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F51" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G51" s="21"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B52" s="5"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F52" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G52" s="21"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B53" s="5"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F53" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G53" s="21"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B54" s="5"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F54" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G54" s="21"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B55" s="5"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="F55" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="G55" s="21"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B56" s="5"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="F56" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="G56" s="21"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B57" s="5"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="F57" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="G57" s="21" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="E12" s="8" t="s">
+      <c r="H57" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="I57" s="5"/>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B58" s="5"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="F58" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="G58" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="H58" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="I58" s="5"/>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B59" s="5"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="F59" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="G59" s="21"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B60" s="5"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="F60" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G60" s="21"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B61" s="5"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="F61" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="G61" s="21"/>
+      <c r="H61" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I61" s="5"/>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B62" s="5"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="F62" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="G62" s="21"/>
+      <c r="H62" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I62" s="5"/>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B63" s="5"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="H12" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="27">
-      <c r="A13" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="F63" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="G63" s="21"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B64" s="5"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="H15" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H18" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F20" s="8" t="s">
+      <c r="F64" s="22" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="H26" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="H32" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="H33" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="H34" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="H35" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="H36" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="H57" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="H58" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="H61" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="H62" s="14" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="A63" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>153</v>
-      </c>
+      <c r="G64" s="21"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I64"/>
@@ -3918,54 +4320,54 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="409.5" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
     </row>
     <row r="3" spans="1:14" ht="381" customHeight="1">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="305">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1232,6 +1232,26 @@
   </si>
   <si>
     <t>不连接适配器去执行的这个点无法实现自动化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已根据检视意见修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不需要修改，见用例批注和提交记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检视通过</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已检视，已修改，已确认</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1353,10 +1373,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1384,6 +1400,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2251,7 +2271,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -2355,7 +2374,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="13" customFormat="1" ht="54" hidden="1">
+    <row r="6" spans="1:6" s="13" customFormat="1" ht="54">
       <c r="A6" s="5" t="s">
         <v>260</v>
       </c>
@@ -2373,7 +2392,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="13" customFormat="1" ht="54" hidden="1">
+    <row r="7" spans="1:6" s="13" customFormat="1" ht="54">
       <c r="A7" s="5" t="s">
         <v>262</v>
       </c>
@@ -2391,7 +2410,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="13" customFormat="1" ht="27" hidden="1">
+    <row r="8" spans="1:6" s="13" customFormat="1" ht="27">
       <c r="A8" s="5" t="s">
         <v>263</v>
       </c>
@@ -2409,7 +2428,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="13" customFormat="1" ht="40.5" hidden="1">
+    <row r="9" spans="1:6" s="13" customFormat="1" ht="40.5">
       <c r="A9" s="5" t="s">
         <v>265</v>
       </c>
@@ -2427,7 +2446,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="13" customFormat="1" ht="40.5" hidden="1">
+    <row r="10" spans="1:6" s="13" customFormat="1" ht="40.5">
       <c r="A10" s="5" t="s">
         <v>266</v>
       </c>
@@ -2445,7 +2464,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="13" customFormat="1" ht="27" hidden="1">
+    <row r="11" spans="1:6" s="13" customFormat="1" ht="27">
       <c r="A11" s="5" t="s">
         <v>267</v>
       </c>
@@ -2499,7 +2518,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="13" customFormat="1" ht="27" hidden="1">
+    <row r="14" spans="1:6" s="13" customFormat="1" ht="27">
       <c r="A14" s="5" t="s">
         <v>273</v>
       </c>
@@ -2515,7 +2534,7 @@
       <c r="E14" s="5"/>
       <c r="F14" s="12"/>
     </row>
-    <row r="15" spans="1:6" s="13" customFormat="1" hidden="1">
+    <row r="15" spans="1:6" s="13" customFormat="1">
       <c r="A15" s="5" t="s">
         <v>274</v>
       </c>
@@ -2531,7 +2550,7 @@
       <c r="E15" s="5"/>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="1:6" s="13" customFormat="1" hidden="1">
+    <row r="16" spans="1:6" s="13" customFormat="1">
       <c r="A16" s="5" t="s">
         <v>275</v>
       </c>
@@ -2547,7 +2566,7 @@
       <c r="E16" s="5"/>
       <c r="F16" s="12"/>
     </row>
-    <row r="17" spans="1:6" s="13" customFormat="1" ht="40.5" hidden="1">
+    <row r="17" spans="1:6" s="13" customFormat="1" ht="40.5">
       <c r="A17" s="5" t="s">
         <v>276</v>
       </c>
@@ -2565,7 +2584,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="18" spans="1:6" s="13" customFormat="1" ht="40.5" hidden="1">
+    <row r="18" spans="1:6" s="13" customFormat="1" ht="40.5">
       <c r="A18" s="5" t="s">
         <v>278</v>
       </c>
@@ -2583,7 +2602,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="13" customFormat="1" ht="27" hidden="1">
+    <row r="19" spans="1:6" s="13" customFormat="1" ht="27">
       <c r="A19" s="5" t="s">
         <v>280</v>
       </c>
@@ -2635,7 +2654,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="22" spans="1:6" s="13" customFormat="1" ht="67.5" hidden="1">
+    <row r="22" spans="1:6" s="13" customFormat="1" ht="67.5">
       <c r="A22" s="5" t="s">
         <v>284</v>
       </c>
@@ -2653,7 +2672,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="23" spans="1:6" s="13" customFormat="1" ht="27" hidden="1">
+    <row r="23" spans="1:6" s="13" customFormat="1" ht="27">
       <c r="A23" s="5" t="s">
         <v>286</v>
       </c>
@@ -2671,7 +2690,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="24" spans="1:6" s="13" customFormat="1" hidden="1">
+    <row r="24" spans="1:6" s="13" customFormat="1">
       <c r="A24" s="5" t="s">
         <v>247</v>
       </c>
@@ -2691,7 +2710,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="25" spans="1:6" s="13" customFormat="1" hidden="1">
+    <row r="25" spans="1:6" s="13" customFormat="1">
       <c r="A25" s="5" t="s">
         <v>290</v>
       </c>
@@ -2717,11 +2736,7 @@
   </sheetData>
   <autoFilter ref="A1:F25">
     <filterColumn colId="2"/>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="黄晓妮"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="3"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2736,39 +2751,39 @@
   <cols>
     <col min="1" max="1" width="14.75" customWidth="1"/>
     <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="4" width="8.625" style="17" customWidth="1"/>
-    <col min="5" max="6" width="9.875" style="24" customWidth="1"/>
-    <col min="7" max="7" width="10.125" style="17" customWidth="1"/>
+    <col min="3" max="4" width="8.625" style="15" customWidth="1"/>
+    <col min="5" max="6" width="9.875" style="22" customWidth="1"/>
+    <col min="7" max="7" width="10.125" style="15" customWidth="1"/>
     <col min="8" max="8" width="37.375" customWidth="1"/>
     <col min="9" max="9" width="39.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="20" customFormat="1" ht="27">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:9" s="18" customFormat="1" ht="27">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="16" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="16" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2777,15 +2792,15 @@
         <v>154</v>
       </c>
       <c r="B2" s="1"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="22" t="s">
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="G2" s="16"/>
+      <c r="G2" s="14"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
@@ -2794,15 +2809,15 @@
         <v>155</v>
       </c>
       <c r="B3" s="5"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="22" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="G3" s="21"/>
+      <c r="G3" s="19"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
@@ -2811,15 +2826,15 @@
         <v>156</v>
       </c>
       <c r="B4" s="5"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="22" t="s">
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="G4" s="21"/>
+      <c r="G4" s="19"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
@@ -2828,15 +2843,15 @@
         <v>157</v>
       </c>
       <c r="B5" s="5"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="22" t="s">
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="G5" s="21"/>
+      <c r="G5" s="19"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
     </row>
@@ -2845,15 +2860,15 @@
         <v>158</v>
       </c>
       <c r="B6" s="5"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="22" t="s">
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="G6" s="21"/>
+      <c r="G6" s="19"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
@@ -2862,15 +2877,15 @@
         <v>159</v>
       </c>
       <c r="B7" s="5"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="22" t="s">
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="G7" s="21"/>
+      <c r="G7" s="19"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
     </row>
@@ -2879,15 +2894,15 @@
         <v>160</v>
       </c>
       <c r="B8" s="5"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="22" t="s">
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="G8" s="21"/>
+      <c r="G8" s="19"/>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
@@ -2896,15 +2911,15 @@
         <v>161</v>
       </c>
       <c r="B9" s="5"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="22" t="s">
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="G9" s="21"/>
+      <c r="G9" s="19"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
     </row>
@@ -2913,19 +2928,19 @@
         <v>162</v>
       </c>
       <c r="B10" s="5"/>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F10" s="23" t="s">
+      <c r="F10" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="G10" s="21"/>
+      <c r="G10" s="19"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5" t="s">
         <v>218</v>
@@ -2936,15 +2951,15 @@
         <v>163</v>
       </c>
       <c r="B11" s="5"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="22" t="s">
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="19" t="s">
         <v>295</v>
       </c>
       <c r="H11" s="12" t="s">
@@ -2957,15 +2972,15 @@
         <v>164</v>
       </c>
       <c r="B12" s="5"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="22" t="s">
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="19" t="s">
         <v>295</v>
       </c>
       <c r="H12" s="12" t="s">
@@ -2978,15 +2993,15 @@
         <v>140</v>
       </c>
       <c r="B13" s="5"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="22" t="s">
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="F13" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="G13" s="21"/>
+      <c r="G13" s="19"/>
       <c r="H13" s="5"/>
       <c r="I13" s="1" t="s">
         <v>299</v>
@@ -2997,15 +3012,15 @@
         <v>165</v>
       </c>
       <c r="B14" s="5"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="22" t="s">
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F14" s="23" t="s">
+      <c r="F14" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="G14" s="21"/>
+      <c r="G14" s="19"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
@@ -3014,15 +3029,15 @@
         <v>166</v>
       </c>
       <c r="B15" s="5"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="22" t="s">
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F15" s="23" t="s">
+      <c r="F15" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="G15" s="21"/>
+      <c r="G15" s="19"/>
       <c r="H15" s="5" t="s">
         <v>294</v>
       </c>
@@ -3033,15 +3048,15 @@
         <v>167</v>
       </c>
       <c r="B16" s="5"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="22" t="s">
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F16" s="23" t="s">
+      <c r="F16" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="G16" s="21"/>
+      <c r="G16" s="19"/>
       <c r="H16" s="5" t="s">
         <v>294</v>
       </c>
@@ -3052,15 +3067,15 @@
         <v>168</v>
       </c>
       <c r="B17" s="5"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="22" t="s">
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F17" s="23" t="s">
+      <c r="F17" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="G17" s="21"/>
+      <c r="G17" s="19"/>
       <c r="H17" s="5" t="s">
         <v>294</v>
       </c>
@@ -3071,15 +3086,15 @@
         <v>169</v>
       </c>
       <c r="B18" s="5"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="22" t="s">
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F18" s="23" t="s">
+      <c r="F18" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="G18" s="21"/>
+      <c r="G18" s="19"/>
       <c r="H18" s="5" t="s">
         <v>294</v>
       </c>
@@ -3090,15 +3105,15 @@
         <v>170</v>
       </c>
       <c r="B19" s="5"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="22" t="s">
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F19" s="23" t="s">
+      <c r="F19" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="G19" s="21"/>
+      <c r="G19" s="19"/>
       <c r="H19" s="5" t="s">
         <v>294</v>
       </c>
@@ -3109,15 +3124,15 @@
         <v>171</v>
       </c>
       <c r="B20" s="5"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="22" t="s">
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G20" s="21"/>
+      <c r="G20" s="19"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
@@ -3126,15 +3141,15 @@
         <v>172</v>
       </c>
       <c r="B21" s="5"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="22" t="s">
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G21" s="21"/>
+      <c r="G21" s="19"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
     </row>
@@ -3143,15 +3158,15 @@
         <v>173</v>
       </c>
       <c r="B22" s="5"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="22" t="s">
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G22" s="21"/>
+      <c r="G22" s="19"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
     </row>
@@ -3160,15 +3175,15 @@
         <v>174</v>
       </c>
       <c r="B23" s="5"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="22" t="s">
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F23" s="22" t="s">
+      <c r="F23" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G23" s="21"/>
+      <c r="G23" s="19"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
     </row>
@@ -3177,15 +3192,15 @@
         <v>175</v>
       </c>
       <c r="B24" s="5"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="22" t="s">
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F24" s="22" t="s">
+      <c r="F24" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G24" s="21"/>
+      <c r="G24" s="19"/>
       <c r="H24" s="5" t="s">
         <v>294</v>
       </c>
@@ -3196,15 +3211,15 @@
         <v>176</v>
       </c>
       <c r="B25" s="5"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="22" t="s">
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F25" s="22" t="s">
+      <c r="F25" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G25" s="21"/>
+      <c r="G25" s="19"/>
       <c r="H25" s="5" t="s">
         <v>294</v>
       </c>
@@ -3215,15 +3230,15 @@
         <v>177</v>
       </c>
       <c r="B26" s="5"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="22" t="s">
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F26" s="22" t="s">
+      <c r="F26" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G26" s="21"/>
+      <c r="G26" s="19"/>
       <c r="H26" s="5" t="s">
         <v>294</v>
       </c>
@@ -3234,15 +3249,15 @@
         <v>178</v>
       </c>
       <c r="B27" s="5"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="22" t="s">
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F27" s="22" t="s">
+      <c r="F27" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G27" s="21"/>
+      <c r="G27" s="19"/>
       <c r="H27" s="5" t="s">
         <v>294</v>
       </c>
@@ -3253,15 +3268,15 @@
         <v>179</v>
       </c>
       <c r="B28" s="5"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="22" t="s">
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F28" s="22" t="s">
+      <c r="F28" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G28" s="21"/>
+      <c r="G28" s="19"/>
       <c r="H28" s="5" t="s">
         <v>294</v>
       </c>
@@ -3272,15 +3287,15 @@
         <v>180</v>
       </c>
       <c r="B29" s="5"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="22" t="s">
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="F29" s="22" t="s">
+      <c r="F29" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G29" s="21"/>
+      <c r="G29" s="19"/>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
     </row>
@@ -3289,15 +3304,15 @@
         <v>181</v>
       </c>
       <c r="B30" s="5"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="22" t="s">
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="F30" s="22" t="s">
+      <c r="F30" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G30" s="21"/>
+      <c r="G30" s="19"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
     </row>
@@ -3306,15 +3321,15 @@
         <v>182</v>
       </c>
       <c r="B31" s="5"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="22" t="s">
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F31" s="22" t="s">
+      <c r="F31" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G31" s="21"/>
+      <c r="G31" s="19"/>
       <c r="H31" s="5" t="s">
         <v>294</v>
       </c>
@@ -3325,15 +3340,15 @@
         <v>183</v>
       </c>
       <c r="B32" s="5"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="22" t="s">
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F32" s="22" t="s">
+      <c r="F32" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G32" s="21"/>
+      <c r="G32" s="19"/>
       <c r="H32" s="5" t="s">
         <v>294</v>
       </c>
@@ -3344,15 +3359,15 @@
         <v>184</v>
       </c>
       <c r="B33" s="5"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="22" t="s">
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F33" s="22" t="s">
+      <c r="F33" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G33" s="21"/>
+      <c r="G33" s="19"/>
       <c r="H33" s="5" t="s">
         <v>294</v>
       </c>
@@ -3363,15 +3378,15 @@
         <v>185</v>
       </c>
       <c r="B34" s="5"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="22" t="s">
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F34" s="22" t="s">
+      <c r="F34" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G34" s="21"/>
+      <c r="G34" s="19"/>
       <c r="H34" s="5" t="s">
         <v>294</v>
       </c>
@@ -3382,15 +3397,15 @@
         <v>186</v>
       </c>
       <c r="B35" s="5"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="22" t="s">
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F35" s="22" t="s">
+      <c r="F35" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="G35" s="21"/>
+      <c r="G35" s="19"/>
       <c r="H35" s="5" t="s">
         <v>294</v>
       </c>
@@ -3401,15 +3416,15 @@
         <v>187</v>
       </c>
       <c r="B36" s="5"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="22" t="s">
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F36" s="22" t="s">
+      <c r="F36" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="G36" s="21"/>
+      <c r="G36" s="19"/>
       <c r="H36" s="5" t="s">
         <v>294</v>
       </c>
@@ -3420,16 +3435,20 @@
         <v>188</v>
       </c>
       <c r="B37" s="5"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="22" t="s">
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F37" s="22" t="s">
+      <c r="F37" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="G37" s="21"/>
-      <c r="H37" s="5"/>
+      <c r="G37" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>304</v>
+      </c>
       <c r="I37" s="5"/>
     </row>
     <row r="38" spans="1:9">
@@ -3437,16 +3456,20 @@
         <v>189</v>
       </c>
       <c r="B38" s="5"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="22" t="s">
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F38" s="22" t="s">
+      <c r="F38" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="G38" s="21"/>
-      <c r="H38" s="5"/>
+      <c r="G38" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>304</v>
+      </c>
       <c r="I38" s="5"/>
     </row>
     <row r="39" spans="1:9">
@@ -3454,16 +3477,20 @@
         <v>190</v>
       </c>
       <c r="B39" s="5"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="22" t="s">
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F39" s="22" t="s">
+      <c r="F39" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="G39" s="21"/>
-      <c r="H39" s="5"/>
+      <c r="G39" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>304</v>
+      </c>
       <c r="I39" s="5"/>
     </row>
     <row r="40" spans="1:9">
@@ -3471,16 +3498,20 @@
         <v>191</v>
       </c>
       <c r="B40" s="5"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="22" t="s">
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F40" s="22" t="s">
+      <c r="F40" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="G40" s="21"/>
-      <c r="H40" s="5"/>
+      <c r="G40" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>304</v>
+      </c>
       <c r="I40" s="5"/>
     </row>
     <row r="41" spans="1:9">
@@ -3488,16 +3519,20 @@
         <v>192</v>
       </c>
       <c r="B41" s="5"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="22" t="s">
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F41" s="22" t="s">
+      <c r="F41" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="G41" s="21"/>
-      <c r="H41" s="5"/>
+      <c r="G41" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>304</v>
+      </c>
       <c r="I41" s="5"/>
     </row>
     <row r="42" spans="1:9">
@@ -3505,16 +3540,18 @@
         <v>193</v>
       </c>
       <c r="B42" s="5"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="22" t="s">
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F42" s="22" t="s">
+      <c r="F42" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G42" s="21"/>
-      <c r="H42" s="5"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="5" t="s">
+        <v>300</v>
+      </c>
       <c r="I42" s="5"/>
     </row>
     <row r="43" spans="1:9">
@@ -3522,16 +3559,18 @@
         <v>194</v>
       </c>
       <c r="B43" s="5"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="22" t="s">
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F43" s="22" t="s">
+      <c r="F43" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G43" s="21"/>
-      <c r="H43" s="5"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="5" t="s">
+        <v>300</v>
+      </c>
       <c r="I43" s="5"/>
     </row>
     <row r="44" spans="1:9">
@@ -3539,16 +3578,18 @@
         <v>195</v>
       </c>
       <c r="B44" s="5"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="22" t="s">
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F44" s="22" t="s">
+      <c r="F44" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G44" s="21"/>
-      <c r="H44" s="5"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="5" t="s">
+        <v>300</v>
+      </c>
       <c r="I44" s="5"/>
     </row>
     <row r="45" spans="1:9">
@@ -3556,16 +3597,18 @@
         <v>196</v>
       </c>
       <c r="B45" s="5"/>
-      <c r="C45" s="21"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="22" t="s">
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F45" s="22" t="s">
+      <c r="F45" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G45" s="21"/>
-      <c r="H45" s="5"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="5" t="s">
+        <v>301</v>
+      </c>
       <c r="I45" s="5"/>
     </row>
     <row r="46" spans="1:9">
@@ -3573,15 +3616,15 @@
         <v>197</v>
       </c>
       <c r="B46" s="5"/>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="22" t="s">
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="F46" s="22" t="s">
+      <c r="F46" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G46" s="21"/>
+      <c r="G46" s="19"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
     </row>
@@ -3590,16 +3633,20 @@
         <v>198</v>
       </c>
       <c r="B47" s="5"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="22" t="s">
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F47" s="22" t="s">
+      <c r="F47" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="G47" s="21"/>
-      <c r="H47" s="5"/>
+      <c r="G47" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>304</v>
+      </c>
       <c r="I47" s="5"/>
     </row>
     <row r="48" spans="1:9">
@@ -3607,16 +3654,20 @@
         <v>199</v>
       </c>
       <c r="B48" s="5"/>
-      <c r="C48" s="21"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="22" t="s">
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F48" s="22" t="s">
+      <c r="F48" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="G48" s="21"/>
-      <c r="H48" s="5"/>
+      <c r="G48" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>304</v>
+      </c>
       <c r="I48" s="5"/>
     </row>
     <row r="49" spans="1:9">
@@ -3624,16 +3675,18 @@
         <v>200</v>
       </c>
       <c r="B49" s="5"/>
-      <c r="C49" s="21"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="22" t="s">
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F49" s="22" t="s">
+      <c r="F49" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G49" s="21"/>
-      <c r="H49" s="5"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="5" t="s">
+        <v>302</v>
+      </c>
       <c r="I49" s="5"/>
     </row>
     <row r="50" spans="1:9">
@@ -3641,16 +3694,18 @@
         <v>201</v>
       </c>
       <c r="B50" s="5"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="22" t="s">
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F50" s="22" t="s">
+      <c r="F50" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G50" s="21"/>
-      <c r="H50" s="5"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="5" t="s">
+        <v>302</v>
+      </c>
       <c r="I50" s="5"/>
     </row>
     <row r="51" spans="1:9">
@@ -3658,16 +3713,18 @@
         <v>202</v>
       </c>
       <c r="B51" s="5"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="22" t="s">
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F51" s="22" t="s">
+      <c r="F51" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G51" s="21"/>
-      <c r="H51" s="5"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="5" t="s">
+        <v>302</v>
+      </c>
       <c r="I51" s="5"/>
     </row>
     <row r="52" spans="1:9">
@@ -3675,16 +3732,18 @@
         <v>203</v>
       </c>
       <c r="B52" s="5"/>
-      <c r="C52" s="21"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="22" t="s">
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F52" s="22" t="s">
+      <c r="F52" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G52" s="21"/>
-      <c r="H52" s="5"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="5" t="s">
+        <v>302</v>
+      </c>
       <c r="I52" s="5"/>
     </row>
     <row r="53" spans="1:9">
@@ -3692,16 +3751,18 @@
         <v>204</v>
       </c>
       <c r="B53" s="5"/>
-      <c r="C53" s="21"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="22" t="s">
+      <c r="C53" s="19"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F53" s="22" t="s">
+      <c r="F53" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G53" s="21"/>
-      <c r="H53" s="5"/>
+      <c r="G53" s="19"/>
+      <c r="H53" s="5" t="s">
+        <v>302</v>
+      </c>
       <c r="I53" s="5"/>
     </row>
     <row r="54" spans="1:9">
@@ -3709,16 +3770,18 @@
         <v>205</v>
       </c>
       <c r="B54" s="5"/>
-      <c r="C54" s="21"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="22" t="s">
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F54" s="22" t="s">
+      <c r="F54" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G54" s="21"/>
-      <c r="H54" s="5"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="5" t="s">
+        <v>302</v>
+      </c>
       <c r="I54" s="5"/>
     </row>
     <row r="55" spans="1:9">
@@ -3726,15 +3789,15 @@
         <v>206</v>
       </c>
       <c r="B55" s="5"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="22" t="s">
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="F55" s="23" t="s">
+      <c r="F55" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="G55" s="21"/>
+      <c r="G55" s="19"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
     </row>
@@ -3743,15 +3806,15 @@
         <v>207</v>
       </c>
       <c r="B56" s="5"/>
-      <c r="C56" s="21"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="22" t="s">
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="F56" s="23" t="s">
+      <c r="F56" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="G56" s="21"/>
+      <c r="G56" s="19"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
     </row>
@@ -3760,15 +3823,15 @@
         <v>208</v>
       </c>
       <c r="B57" s="5"/>
-      <c r="C57" s="21"/>
-      <c r="D57" s="21"/>
-      <c r="E57" s="22" t="s">
+      <c r="C57" s="19"/>
+      <c r="D57" s="19"/>
+      <c r="E57" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="F57" s="22" t="s">
+      <c r="F57" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G57" s="21" t="s">
+      <c r="G57" s="19" t="s">
         <v>295</v>
       </c>
       <c r="H57" s="12" t="s">
@@ -3781,15 +3844,15 @@
         <v>209</v>
       </c>
       <c r="B58" s="5"/>
-      <c r="C58" s="21"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="22" t="s">
+      <c r="C58" s="19"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="F58" s="22" t="s">
+      <c r="F58" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G58" s="21" t="s">
+      <c r="G58" s="19" t="s">
         <v>295</v>
       </c>
       <c r="H58" s="12" t="s">
@@ -3802,15 +3865,15 @@
         <v>210</v>
       </c>
       <c r="B59" s="5"/>
-      <c r="C59" s="21"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="22" t="s">
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="F59" s="22" t="s">
+      <c r="F59" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G59" s="21"/>
+      <c r="G59" s="19"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
     </row>
@@ -3819,15 +3882,15 @@
         <v>211</v>
       </c>
       <c r="B60" s="5"/>
-      <c r="C60" s="21"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="22" t="s">
+      <c r="C60" s="19"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="F60" s="22" t="s">
+      <c r="F60" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="G60" s="21"/>
+      <c r="G60" s="19"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
     </row>
@@ -3836,15 +3899,15 @@
         <v>212</v>
       </c>
       <c r="B61" s="5"/>
-      <c r="C61" s="21"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="22" t="s">
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="F61" s="22" t="s">
+      <c r="F61" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G61" s="21"/>
+      <c r="G61" s="19"/>
       <c r="H61" s="5" t="s">
         <v>294</v>
       </c>
@@ -3855,15 +3918,15 @@
         <v>213</v>
       </c>
       <c r="B62" s="5"/>
-      <c r="C62" s="21"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="22" t="s">
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="F62" s="22" t="s">
+      <c r="F62" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G62" s="21"/>
+      <c r="G62" s="19"/>
       <c r="H62" s="5" t="s">
         <v>294</v>
       </c>
@@ -3874,15 +3937,15 @@
         <v>214</v>
       </c>
       <c r="B63" s="5"/>
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="22" t="s">
+      <c r="C63" s="19"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="F63" s="22" t="s">
+      <c r="F63" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="G63" s="21"/>
+      <c r="G63" s="19"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
     </row>
@@ -3891,15 +3954,15 @@
         <v>215</v>
       </c>
       <c r="B64" s="5"/>
-      <c r="C64" s="21"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="22" t="s">
+      <c r="C64" s="19"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="F64" s="22" t="s">
+      <c r="F64" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="G64" s="21"/>
+      <c r="G64" s="19"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
     </row>
@@ -4320,40 +4383,40 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="409.5" customHeight="1">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
     </row>
     <row r="3" spans="1:14" ht="381" customHeight="1">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="8" t="s">

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="304">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1240,10 +1240,6 @@
   </si>
   <si>
     <t>不需要修改，见用例批注和提交记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检视通过</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2746,6 +2742,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I64"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -2787,7 +2784,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" hidden="1">
       <c r="A2" s="5" t="s">
         <v>154</v>
       </c>
@@ -2804,7 +2801,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" hidden="1">
       <c r="A3" s="5" t="s">
         <v>155</v>
       </c>
@@ -2821,7 +2818,7 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" hidden="1">
       <c r="A4" s="5" t="s">
         <v>156</v>
       </c>
@@ -2838,7 +2835,7 @@
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" hidden="1">
       <c r="A5" s="5" t="s">
         <v>157</v>
       </c>
@@ -2855,7 +2852,7 @@
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" hidden="1">
       <c r="A6" s="5" t="s">
         <v>158</v>
       </c>
@@ -2872,7 +2869,7 @@
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" hidden="1">
       <c r="A7" s="5" t="s">
         <v>159</v>
       </c>
@@ -2889,7 +2886,7 @@
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" hidden="1">
       <c r="A8" s="5" t="s">
         <v>160</v>
       </c>
@@ -2906,7 +2903,7 @@
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" hidden="1">
       <c r="A9" s="5" t="s">
         <v>161</v>
       </c>
@@ -2923,7 +2920,7 @@
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" hidden="1">
       <c r="A10" s="5" t="s">
         <v>162</v>
       </c>
@@ -2946,7 +2943,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" hidden="1">
       <c r="A11" s="5" t="s">
         <v>163</v>
       </c>
@@ -2967,7 +2964,7 @@
       </c>
       <c r="I11" s="5"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" hidden="1">
       <c r="A12" s="5" t="s">
         <v>164</v>
       </c>
@@ -2988,7 +2985,7 @@
       </c>
       <c r="I12" s="5"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" hidden="1">
       <c r="A13" s="5" t="s">
         <v>140</v>
       </c>
@@ -3007,7 +3004,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" hidden="1">
       <c r="A14" s="5" t="s">
         <v>165</v>
       </c>
@@ -3024,7 +3021,7 @@
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" hidden="1">
       <c r="A15" s="5" t="s">
         <v>166</v>
       </c>
@@ -3043,7 +3040,7 @@
       </c>
       <c r="I15" s="5"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" hidden="1">
       <c r="A16" s="5" t="s">
         <v>167</v>
       </c>
@@ -3062,7 +3059,7 @@
       </c>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" hidden="1">
       <c r="A17" s="5" t="s">
         <v>168</v>
       </c>
@@ -3081,7 +3078,7 @@
       </c>
       <c r="I17" s="5"/>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" hidden="1">
       <c r="A18" s="5" t="s">
         <v>169</v>
       </c>
@@ -3100,7 +3097,7 @@
       </c>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" hidden="1">
       <c r="A19" s="5" t="s">
         <v>170</v>
       </c>
@@ -3119,7 +3116,7 @@
       </c>
       <c r="I19" s="5"/>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" hidden="1">
       <c r="A20" s="5" t="s">
         <v>171</v>
       </c>
@@ -3136,7 +3133,7 @@
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" hidden="1">
       <c r="A21" s="5" t="s">
         <v>172</v>
       </c>
@@ -3153,7 +3150,7 @@
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" hidden="1">
       <c r="A22" s="5" t="s">
         <v>173</v>
       </c>
@@ -3170,7 +3167,7 @@
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" hidden="1">
       <c r="A23" s="5" t="s">
         <v>174</v>
       </c>
@@ -3187,7 +3184,7 @@
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" hidden="1">
       <c r="A24" s="5" t="s">
         <v>175</v>
       </c>
@@ -3206,7 +3203,7 @@
       </c>
       <c r="I24" s="5"/>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" hidden="1">
       <c r="A25" s="5" t="s">
         <v>176</v>
       </c>
@@ -3225,7 +3222,7 @@
       </c>
       <c r="I25" s="5"/>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" hidden="1">
       <c r="A26" s="5" t="s">
         <v>177</v>
       </c>
@@ -3244,7 +3241,7 @@
       </c>
       <c r="I26" s="5"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" hidden="1">
       <c r="A27" s="5" t="s">
         <v>178</v>
       </c>
@@ -3263,7 +3260,7 @@
       </c>
       <c r="I27" s="5"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" hidden="1">
       <c r="A28" s="5" t="s">
         <v>179</v>
       </c>
@@ -3282,7 +3279,7 @@
       </c>
       <c r="I28" s="5"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" hidden="1">
       <c r="A29" s="5" t="s">
         <v>180</v>
       </c>
@@ -3299,7 +3296,7 @@
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" hidden="1">
       <c r="A30" s="5" t="s">
         <v>181</v>
       </c>
@@ -3316,7 +3313,7 @@
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" hidden="1">
       <c r="A31" s="5" t="s">
         <v>182</v>
       </c>
@@ -3335,7 +3332,7 @@
       </c>
       <c r="I31" s="5"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" hidden="1">
       <c r="A32" s="5" t="s">
         <v>183</v>
       </c>
@@ -3354,7 +3351,7 @@
       </c>
       <c r="I32" s="5"/>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" hidden="1">
       <c r="A33" s="5" t="s">
         <v>184</v>
       </c>
@@ -3373,7 +3370,7 @@
       </c>
       <c r="I33" s="5"/>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" hidden="1">
       <c r="A34" s="5" t="s">
         <v>185</v>
       </c>
@@ -3392,7 +3389,7 @@
       </c>
       <c r="I34" s="5"/>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" hidden="1">
       <c r="A35" s="5" t="s">
         <v>186</v>
       </c>
@@ -3411,7 +3408,7 @@
       </c>
       <c r="I35" s="5"/>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" hidden="1">
       <c r="A36" s="5" t="s">
         <v>187</v>
       </c>
@@ -3444,10 +3441,10 @@
         <v>152</v>
       </c>
       <c r="G37" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="H37" s="5" t="s">
         <v>303</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>304</v>
       </c>
       <c r="I37" s="5"/>
     </row>
@@ -3465,10 +3462,10 @@
         <v>152</v>
       </c>
       <c r="G38" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="H38" s="5" t="s">
         <v>303</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>304</v>
       </c>
       <c r="I38" s="5"/>
     </row>
@@ -3486,10 +3483,10 @@
         <v>152</v>
       </c>
       <c r="G39" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="H39" s="5" t="s">
         <v>303</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>304</v>
       </c>
       <c r="I39" s="5"/>
     </row>
@@ -3507,10 +3504,10 @@
         <v>152</v>
       </c>
       <c r="G40" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="H40" s="5" t="s">
         <v>303</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>304</v>
       </c>
       <c r="I40" s="5"/>
     </row>
@@ -3528,10 +3525,10 @@
         <v>152</v>
       </c>
       <c r="G41" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="H41" s="5" t="s">
         <v>303</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>304</v>
       </c>
       <c r="I41" s="5"/>
     </row>
@@ -3611,7 +3608,7 @@
       </c>
       <c r="I45" s="5"/>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" hidden="1">
       <c r="A46" s="5" t="s">
         <v>197</v>
       </c>
@@ -3642,10 +3639,10 @@
         <v>152</v>
       </c>
       <c r="G47" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="H47" s="5" t="s">
         <v>303</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>304</v>
       </c>
       <c r="I47" s="5"/>
     </row>
@@ -3663,10 +3660,10 @@
         <v>152</v>
       </c>
       <c r="G48" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="H48" s="5" t="s">
         <v>303</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>304</v>
       </c>
       <c r="I48" s="5"/>
     </row>
@@ -3684,9 +3681,7 @@
         <v>151</v>
       </c>
       <c r="G49" s="19"/>
-      <c r="H49" s="5" t="s">
-        <v>302</v>
-      </c>
+      <c r="H49" s="5"/>
       <c r="I49" s="5"/>
     </row>
     <row r="50" spans="1:9">
@@ -3703,9 +3698,7 @@
         <v>151</v>
       </c>
       <c r="G50" s="19"/>
-      <c r="H50" s="5" t="s">
-        <v>302</v>
-      </c>
+      <c r="H50" s="5"/>
       <c r="I50" s="5"/>
     </row>
     <row r="51" spans="1:9">
@@ -3722,9 +3715,7 @@
         <v>151</v>
       </c>
       <c r="G51" s="19"/>
-      <c r="H51" s="5" t="s">
-        <v>302</v>
-      </c>
+      <c r="H51" s="5"/>
       <c r="I51" s="5"/>
     </row>
     <row r="52" spans="1:9">
@@ -3741,9 +3732,7 @@
         <v>151</v>
       </c>
       <c r="G52" s="19"/>
-      <c r="H52" s="5" t="s">
-        <v>302</v>
-      </c>
+      <c r="H52" s="5"/>
       <c r="I52" s="5"/>
     </row>
     <row r="53" spans="1:9">
@@ -3760,9 +3749,7 @@
         <v>151</v>
       </c>
       <c r="G53" s="19"/>
-      <c r="H53" s="5" t="s">
-        <v>302</v>
-      </c>
+      <c r="H53" s="5"/>
       <c r="I53" s="5"/>
     </row>
     <row r="54" spans="1:9">
@@ -3779,12 +3766,10 @@
         <v>151</v>
       </c>
       <c r="G54" s="19"/>
-      <c r="H54" s="5" t="s">
-        <v>302</v>
-      </c>
+      <c r="H54" s="5"/>
       <c r="I54" s="5"/>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" hidden="1">
       <c r="A55" s="5" t="s">
         <v>206</v>
       </c>
@@ -3801,7 +3786,7 @@
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" hidden="1">
       <c r="A56" s="5" t="s">
         <v>207</v>
       </c>
@@ -3818,7 +3803,7 @@
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" hidden="1">
       <c r="A57" s="5" t="s">
         <v>208</v>
       </c>
@@ -3839,7 +3824,7 @@
       </c>
       <c r="I57" s="5"/>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" hidden="1">
       <c r="A58" s="5" t="s">
         <v>209</v>
       </c>
@@ -3860,7 +3845,7 @@
       </c>
       <c r="I58" s="5"/>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" hidden="1">
       <c r="A59" s="5" t="s">
         <v>210</v>
       </c>
@@ -3877,7 +3862,7 @@
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" hidden="1">
       <c r="A60" s="5" t="s">
         <v>211</v>
       </c>
@@ -3894,7 +3879,7 @@
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" hidden="1">
       <c r="A61" s="5" t="s">
         <v>212</v>
       </c>
@@ -3913,7 +3898,7 @@
       </c>
       <c r="I61" s="5"/>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" hidden="1">
       <c r="A62" s="5" t="s">
         <v>213</v>
       </c>
@@ -3932,7 +3917,7 @@
       </c>
       <c r="I62" s="5"/>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" hidden="1">
       <c r="A63" s="5" t="s">
         <v>214</v>
       </c>
@@ -3949,7 +3934,7 @@
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" hidden="1">
       <c r="A64" s="5" t="s">
         <v>215</v>
       </c>
@@ -3967,7 +3952,13 @@
       <c r="I64" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I64"/>
+  <autoFilter ref="A1:I64">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="黄晓妮"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
+++ b/internal_doc/05.测试设计/story/FullTextSearch/自动化用例实现跟踪表.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="306">
   <si>
     <t>用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -995,10 +995,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>赵小妮/赵育</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3.全文索引正常同步的流程，也可能存在索引删除重建的(比如pop固定集合超时)，后面需要优化数据同步的公共方法</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1028,6 +1024,215 @@
   </si>
   <si>
     <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-11988</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尹臻/刘晓璇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-11989</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-11990</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-11995</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卢伟康</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12018</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12019</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.truncate集合的时候，需要修改调用修改后的公共方法
+2.teardown里面统一校验下固定集合、ES是否残留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12065</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-12066</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14372</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14374</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、代码逻辑不够清晰，建议优化，见用例批注
+2、很多db.close不规范的哦（公共问题）
+3、检查结果同12015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14376</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、代码貌似跟 14374 没区别（一个时es没数据，一个时数据处理中，但是代码层面看不出区别，且测试点怎么保证有测到点上？）
+2、其他同14374</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14377</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14397</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14398</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-14885</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正在查询固定集合时删除全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-15799</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主表执行truncate清空记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全量同步时，删除原始集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与用例11981重复，对应手工用例及自动化用例需删除(已删除)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seqDB-18260</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增量同步时，删除原始集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检视责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不连接适配器去执行的这个点无法实现自动化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已根据检视意见修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不需要修改，见用例批注和提交记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已检视，已修改，已确认</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、文本用例测的是“加入域”并自动切分，自动化用例没有域和自动切分，测试点没测到
+2、其他问题同 seqDB-11981
+2015/05/29：已确认修改，需再次修改，见用例批注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、测试点不清晰，见用例注释
+2、删除索引没有校验节点间数据一致性
+2015/05/29：已确认修改，需再次修改，见用例批注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、判断组个数统一用CommLib.OneGroupMode
+2、插入数据无特殊场景考虑，建议使用公共方法
+3、teardown删除cl需要使用公共方法，另外关闭sdb和es连接需要放到finally
+4、teardown需要添加固定集合是否残留的检查（赵育新加的规范：所有用例teardown都需要检查固定集合和索引是否有残留）
+2015/05/29：已确认修改，需再次修改，见用例批注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同 12020
+2015/05/29：已确认修改，需再次修改，见用例批注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已检视，见用例批注。已修改。已确认。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尹臻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵小妮</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1037,23 +1242,8 @@
 4、部分代码多且多次调用的建议另写私有方法调用
 5、insertData没有特殊考虑建议使用公共方法FullTextDBUtils.insertData
 6、sdb、esClient关闭连接统一加上 !=null 的判断
-7、teardown里面的连接需要放到finally里面，否则前面有步骤执行失败不会走到关闭连接，连接残留</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-11988</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>尹臻/刘晓璇</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-11989</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-11990</t>
+7、teardown里面的连接需要放到finally里面，否则前面有步骤执行失败不会走到关闭连接，连接残留
+2019/5/31:再次检视通过</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1062,192 +1252,17 @@
 2、1个组上多个子表的场景没有覆盖到
 3、插入数据和创建索引测试点有些乱，见用例批注
 4、插入数据建议改为使用公共方法FullTextDBUtils.insertData
-5、不需要先删除所有子表再删主表，删除主表会同时删除主表下挂载的子表（主子表公共问题）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-11995</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>卢伟康</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12015</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12016</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>赵育</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12017</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12018</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12019</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.truncate集合的时候，需要修改调用修改后的公共方法
-2.teardown里面统一校验下固定集合、ES是否残留</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12020</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、判断组个数统一用CommLib.OneGroupMode
-2、插入数据无特殊场景考虑，建议使用公共方法
-3、teardown删除cl需要使用公共方法，另外关闭sdb和es连接需要放到finally
-4、teardown需要添加固定集合是否残留的检查（赵育新加的规范：所有用例teardown都需要检查固定集合和索引是否有残留）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同 12020</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12065</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-12066</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-14372</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-14374</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、代码逻辑不够清晰，建议优化，见用例批注
-2、很多db.close不规范的哦（公共问题）
-3、检查结果同12015</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-14376</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、代码貌似跟 14374 没区别（一个时es没数据，一个时数据处理中，但是代码层面看不出区别，且测试点怎么保证有测到点上？）
-2、其他同14374</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-14377</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-14397</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同 11981，测试点有些乱，需要重新梳理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-14398</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-14885</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>正在查询固定集合时删除全文索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-15799</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主表执行truncate清空记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全量同步时，删除原始集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>与用例11981重复，对应手工用例及自动化用例需删除(已删除)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>seqDB-18260</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增量同步时，删除原始集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、文本用例测的是“加入域”并自动切分，自动化用例没有域和自动切分，测试点没测到
-2、其他问题同 seqDB-11981</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、测试点不清晰，见用例注释
-2、删除索引没有校验节点间数据一致性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已检视，见用例批注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例责任人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检视责任人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已检视，见用例批注。再次检视完成。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不连接适配器去执行的这个点无法实现自动化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已根据检视意见修改</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不需要修改，见用例批注和提交记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已检视，已修改，已确认</t>
+5、不需要先删除所有子表再删主表，删除主表会同时删除主表下挂载的子表（主子表公共问题）
+2019/5/31:再次检视通过</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同 11981，测试点有些乱，需要重新梳理
+2019/5/31:再次检视通过</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已检视，见用例批注。再次检视，见用例批注。已修改。已确认。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1340,7 +1355,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1359,9 +1374,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1399,7 +1411,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2274,7 +2292,7 @@
     <col min="2" max="2" width="33.875" customWidth="1"/>
     <col min="3" max="3" width="14.125" style="8" customWidth="1"/>
     <col min="4" max="4" width="11.75" customWidth="1"/>
-    <col min="5" max="5" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="9.375" style="14" customWidth="1"/>
     <col min="6" max="6" width="84.625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2291,72 +2309,78 @@
       <c r="D1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="25" t="s">
         <v>153</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="13" customFormat="1" ht="148.5">
+    <row r="2" spans="1:6" s="12" customFormat="1" ht="162">
       <c r="A2" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="C2" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="12" customFormat="1" ht="40.5">
+      <c r="A3" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="12" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="13" customFormat="1" ht="27">
-      <c r="A3" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>221</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>256</v>
+        <v>300</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="12" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="13" customFormat="1" ht="27">
+      <c r="E3" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="12" customFormat="1" ht="40.5">
       <c r="A4" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B4" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>222</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>256</v>
+        <v>300</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="12" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="13" customFormat="1" ht="81">
+      <c r="E4" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="12" customFormat="1" ht="94.5">
       <c r="A5" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="B5" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>223</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -2365,260 +2389,266 @@
       <c r="D5" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="12" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="13" customFormat="1" ht="54">
+      <c r="E5" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="12" customFormat="1" ht="54">
       <c r="A6" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="B6" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>224</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>219</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E6" s="18"/>
+      <c r="F6" s="11" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="13" customFormat="1" ht="54">
+    <row r="7" spans="1:6" s="12" customFormat="1" ht="54">
       <c r="A7" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B7" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>225</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>219</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E7" s="18"/>
+      <c r="F7" s="11" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="13" customFormat="1" ht="27">
+    <row r="8" spans="1:6" s="12" customFormat="1" ht="27">
       <c r="A8" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="B8" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>226</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>219</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="E8" s="18"/>
+      <c r="F8" s="11" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="13" customFormat="1" ht="40.5">
+    <row r="9" spans="1:6" s="12" customFormat="1" ht="40.5">
       <c r="A9" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B9" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>227</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>219</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="E9" s="18"/>
+      <c r="F9" s="11" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="13" customFormat="1" ht="40.5">
+    <row r="10" spans="1:6" s="12" customFormat="1" ht="40.5">
       <c r="A10" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B10" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>219</v>
       </c>
       <c r="D10" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E10" s="18"/>
+      <c r="F10" s="11" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="12" customFormat="1" ht="27">
+      <c r="A11" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="12" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="13" customFormat="1" ht="27">
-      <c r="A11" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>229</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>219</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="12" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="13" customFormat="1" ht="67.5">
+        <v>261</v>
+      </c>
+      <c r="E11" s="18"/>
+      <c r="F11" s="11" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="12" customFormat="1" ht="81">
       <c r="A12" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="B12" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>230</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>245</v>
+        <v>301</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="12" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" s="13" customFormat="1" ht="27">
+      <c r="E12" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="12" customFormat="1" ht="27">
       <c r="A13" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="B13" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>231</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>245</v>
+        <v>301</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="12" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="13" customFormat="1" ht="27">
+      <c r="E13" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="12" customFormat="1" ht="27">
       <c r="A14" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="B14" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>232</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="12"/>
-    </row>
-    <row r="15" spans="1:6" s="13" customFormat="1">
+        <v>258</v>
+      </c>
+      <c r="E14" s="18"/>
+      <c r="F14" s="11"/>
+    </row>
+    <row r="15" spans="1:6" s="12" customFormat="1">
       <c r="A15" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="B15" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>233</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="12"/>
-    </row>
-    <row r="16" spans="1:6" s="13" customFormat="1">
+        <v>258</v>
+      </c>
+      <c r="E15" s="18"/>
+      <c r="F15" s="11"/>
+    </row>
+    <row r="16" spans="1:6" s="12" customFormat="1">
       <c r="A16" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="B16" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>234</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="12"/>
-    </row>
-    <row r="17" spans="1:6" s="13" customFormat="1" ht="40.5">
+        <v>258</v>
+      </c>
+      <c r="E16" s="18"/>
+      <c r="F16" s="11"/>
+    </row>
+    <row r="17" spans="1:6" s="12" customFormat="1" ht="40.5">
       <c r="A17" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="B17" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>235</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>219</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="12" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" s="13" customFormat="1" ht="40.5">
+        <v>258</v>
+      </c>
+      <c r="E17" s="18"/>
+      <c r="F17" s="11" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="12" customFormat="1" ht="40.5">
       <c r="A18" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B18" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>236</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>219</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="12" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="13" customFormat="1" ht="27">
+        <v>258</v>
+      </c>
+      <c r="E18" s="18"/>
+      <c r="F18" s="11" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="12" customFormat="1" ht="27">
       <c r="A19" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="B19" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>237</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>219</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="12"/>
-    </row>
-    <row r="20" spans="1:6" s="13" customFormat="1">
+        <v>258</v>
+      </c>
+      <c r="E19" s="18"/>
+      <c r="F19" s="11"/>
+    </row>
+    <row r="20" spans="1:6" s="12" customFormat="1" ht="27">
       <c r="A20" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="B20" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>238</v>
       </c>
       <c r="C20" s="5" t="s">
@@ -2627,16 +2657,18 @@
       <c r="D20" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="12" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" s="13" customFormat="1">
+      <c r="E20" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="12" customFormat="1" ht="27">
       <c r="A21" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="B21" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>239</v>
       </c>
       <c r="C21" s="5" t="s">
@@ -2645,85 +2677,87 @@
       <c r="D21" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="12" t="s">
+      <c r="E21" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="12" customFormat="1" ht="67.5">
+      <c r="A22" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E22" s="18"/>
+      <c r="F22" s="11" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="12" customFormat="1" ht="27">
+      <c r="A23" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E23" s="18"/>
+      <c r="F23" s="11" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" s="12" customFormat="1">
+      <c r="A24" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" s="13" customFormat="1" ht="67.5">
-      <c r="A22" s="5" t="s">
+      <c r="C24" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" s="12" customFormat="1">
+      <c r="A25" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B25" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" s="13" customFormat="1" ht="27">
-      <c r="A23" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="12" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" s="13" customFormat="1">
-      <c r="A24" s="5" t="s">
+      <c r="C25" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E25" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="B24" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="E24" s="5" t="s">
+      <c r="F25" s="11" t="s">
         <v>248</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" s="13" customFormat="1">
-      <c r="A25" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2742,688 +2776,719 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I64"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.75" customWidth="1"/>
     <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="4" width="8.625" style="15" customWidth="1"/>
-    <col min="5" max="6" width="9.875" style="22" customWidth="1"/>
-    <col min="7" max="7" width="10.125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="37.375" customWidth="1"/>
+    <col min="3" max="4" width="8.625" style="14" customWidth="1"/>
+    <col min="5" max="6" width="9.875" style="21" customWidth="1"/>
+    <col min="7" max="7" width="9" style="14" customWidth="1"/>
+    <col min="8" max="8" width="41.75" style="22" customWidth="1"/>
     <col min="9" max="9" width="39.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="18" customFormat="1" ht="27">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:9" s="17" customFormat="1" ht="27">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="G1" s="17" t="s">
+      <c r="E1" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="G1" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="15" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1">
+    <row r="2" spans="1:9">
       <c r="A2" s="5" t="s">
         <v>154</v>
       </c>
       <c r="B2" s="1"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="20" t="s">
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G2" s="14"/>
+      <c r="G2" s="13"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" hidden="1">
+    <row r="3" spans="1:9">
       <c r="A3" s="5" t="s">
         <v>155</v>
       </c>
       <c r="B3" s="5"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="20" t="s">
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G3" s="19"/>
+      <c r="G3" s="18"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:9" hidden="1">
+    <row r="4" spans="1:9">
       <c r="A4" s="5" t="s">
         <v>156</v>
       </c>
       <c r="B4" s="5"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="20" t="s">
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G4" s="19"/>
+      <c r="G4" s="18"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" spans="1:9" hidden="1">
+    <row r="5" spans="1:9">
       <c r="A5" s="5" t="s">
         <v>157</v>
       </c>
       <c r="B5" s="5"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="20" t="s">
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G5" s="19"/>
+      <c r="G5" s="18"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9" hidden="1">
+    <row r="6" spans="1:9">
       <c r="A6" s="5" t="s">
         <v>158</v>
       </c>
       <c r="B6" s="5"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="20" t="s">
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G6" s="19"/>
+      <c r="G6" s="18"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" spans="1:9" hidden="1">
+    <row r="7" spans="1:9">
       <c r="A7" s="5" t="s">
         <v>159</v>
       </c>
       <c r="B7" s="5"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="20" t="s">
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="G7" s="19"/>
+      <c r="G7" s="18"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
     </row>
-    <row r="8" spans="1:9" hidden="1">
+    <row r="8" spans="1:9">
       <c r="A8" s="5" t="s">
         <v>160</v>
       </c>
       <c r="B8" s="5"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="20" t="s">
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="G8" s="19"/>
+      <c r="G8" s="18"/>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" spans="1:9" hidden="1">
+    <row r="9" spans="1:9">
       <c r="A9" s="5" t="s">
         <v>161</v>
       </c>
       <c r="B9" s="5"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="20" t="s">
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="G9" s="19"/>
+      <c r="G9" s="18"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
     </row>
-    <row r="10" spans="1:9" hidden="1">
+    <row r="10" spans="1:9">
       <c r="A10" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B10" s="5"/>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="G10" s="19"/>
+      <c r="G10" s="18"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1">
+    <row r="11" spans="1:9">
       <c r="A11" s="5" t="s">
         <v>163</v>
       </c>
       <c r="B11" s="5"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="20" t="s">
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G11" s="19" t="s">
-        <v>295</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>298</v>
+      <c r="G11" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>299</v>
       </c>
       <c r="I11" s="5"/>
     </row>
-    <row r="12" spans="1:9" hidden="1">
+    <row r="12" spans="1:9">
       <c r="A12" s="5" t="s">
         <v>164</v>
       </c>
       <c r="B12" s="5"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="20" t="s">
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="F12" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G12" s="19" t="s">
-        <v>295</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>298</v>
+      <c r="G12" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>299</v>
       </c>
       <c r="I12" s="5"/>
     </row>
-    <row r="13" spans="1:9" hidden="1">
+    <row r="13" spans="1:9">
       <c r="A13" s="5" t="s">
         <v>140</v>
       </c>
       <c r="B13" s="5"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="20" t="s">
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="G13" s="19"/>
+      <c r="G13" s="18"/>
       <c r="H13" s="5"/>
       <c r="I13" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" hidden="1">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="5" t="s">
         <v>165</v>
       </c>
       <c r="B14" s="5"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="20" t="s">
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F14" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="G14" s="19"/>
+      <c r="G14" s="18"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
-    <row r="15" spans="1:9" hidden="1">
+    <row r="15" spans="1:9">
       <c r="A15" s="5" t="s">
         <v>166</v>
       </c>
       <c r="B15" s="5"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="20" t="s">
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F15" s="21" t="s">
+      <c r="F15" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G15" s="19"/>
-      <c r="H15" s="5" t="s">
-        <v>294</v>
+      <c r="G15" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>299</v>
       </c>
       <c r="I15" s="5"/>
     </row>
-    <row r="16" spans="1:9" hidden="1">
+    <row r="16" spans="1:9">
       <c r="A16" s="5" t="s">
         <v>167</v>
       </c>
       <c r="B16" s="5"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="20" t="s">
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F16" s="21" t="s">
+      <c r="F16" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G16" s="19"/>
-      <c r="H16" s="5" t="s">
-        <v>294</v>
+      <c r="G16" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>299</v>
       </c>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" spans="1:9" hidden="1">
+    <row r="17" spans="1:9">
       <c r="A17" s="5" t="s">
         <v>168</v>
       </c>
       <c r="B17" s="5"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="20" t="s">
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="F17" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G17" s="19"/>
-      <c r="H17" s="5" t="s">
-        <v>294</v>
+      <c r="G17" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>299</v>
       </c>
       <c r="I17" s="5"/>
     </row>
-    <row r="18" spans="1:9" hidden="1">
+    <row r="18" spans="1:9">
       <c r="A18" s="5" t="s">
         <v>169</v>
       </c>
       <c r="B18" s="5"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="20" t="s">
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F18" s="21" t="s">
+      <c r="F18" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G18" s="19"/>
-      <c r="H18" s="5" t="s">
-        <v>294</v>
+      <c r="G18" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>299</v>
       </c>
       <c r="I18" s="5"/>
     </row>
-    <row r="19" spans="1:9" hidden="1">
+    <row r="19" spans="1:9">
       <c r="A19" s="5" t="s">
         <v>170</v>
       </c>
       <c r="B19" s="5"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="20" t="s">
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="F19" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="G19" s="19"/>
-      <c r="H19" s="5" t="s">
-        <v>294</v>
+      <c r="G19" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>299</v>
       </c>
       <c r="I19" s="5"/>
     </row>
-    <row r="20" spans="1:9" hidden="1">
+    <row r="20" spans="1:9">
       <c r="A20" s="5" t="s">
         <v>171</v>
       </c>
       <c r="B20" s="5"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="20" t="s">
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="F20" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G20" s="19"/>
+      <c r="G20" s="18"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
-    <row r="21" spans="1:9" hidden="1">
+    <row r="21" spans="1:9">
       <c r="A21" s="5" t="s">
         <v>172</v>
       </c>
       <c r="B21" s="5"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="20" t="s">
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="F21" s="20" t="s">
+      <c r="F21" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G21" s="19"/>
+      <c r="G21" s="18"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
     </row>
-    <row r="22" spans="1:9" hidden="1">
+    <row r="22" spans="1:9">
       <c r="A22" s="5" t="s">
         <v>173</v>
       </c>
       <c r="B22" s="5"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="20" t="s">
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="F22" s="20" t="s">
+      <c r="F22" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G22" s="19"/>
+      <c r="G22" s="18"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
     </row>
-    <row r="23" spans="1:9" hidden="1">
+    <row r="23" spans="1:9">
       <c r="A23" s="5" t="s">
         <v>174</v>
       </c>
       <c r="B23" s="5"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="20" t="s">
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="F23" s="20" t="s">
+      <c r="F23" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G23" s="19"/>
+      <c r="G23" s="18"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
     </row>
-    <row r="24" spans="1:9" hidden="1">
+    <row r="24" spans="1:9" ht="27">
       <c r="A24" s="5" t="s">
         <v>175</v>
       </c>
       <c r="B24" s="5"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="20" t="s">
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="F24" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="G24" s="19"/>
-      <c r="H24" s="5" t="s">
-        <v>294</v>
+      <c r="G24" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>305</v>
       </c>
       <c r="I24" s="5"/>
     </row>
-    <row r="25" spans="1:9" hidden="1">
+    <row r="25" spans="1:9" ht="27">
       <c r="A25" s="5" t="s">
         <v>176</v>
       </c>
       <c r="B25" s="5"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="20" t="s">
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="F25" s="20" t="s">
+      <c r="F25" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="G25" s="19"/>
-      <c r="H25" s="5" t="s">
-        <v>294</v>
+      <c r="G25" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>305</v>
       </c>
       <c r="I25" s="5"/>
     </row>
-    <row r="26" spans="1:9" hidden="1">
+    <row r="26" spans="1:9" ht="27">
       <c r="A26" s="5" t="s">
         <v>177</v>
       </c>
       <c r="B26" s="5"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="20" t="s">
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="F26" s="20" t="s">
+      <c r="F26" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="G26" s="19"/>
-      <c r="H26" s="5" t="s">
-        <v>294</v>
+      <c r="G26" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>305</v>
       </c>
       <c r="I26" s="5"/>
     </row>
-    <row r="27" spans="1:9" hidden="1">
+    <row r="27" spans="1:9" ht="27">
       <c r="A27" s="5" t="s">
         <v>178</v>
       </c>
       <c r="B27" s="5"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="20" t="s">
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="F27" s="20" t="s">
+      <c r="F27" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="G27" s="19"/>
-      <c r="H27" s="5" t="s">
-        <v>294</v>
+      <c r="G27" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>305</v>
       </c>
       <c r="I27" s="5"/>
     </row>
-    <row r="28" spans="1:9" hidden="1">
+    <row r="28" spans="1:9" ht="27">
       <c r="A28" s="5" t="s">
         <v>179</v>
       </c>
       <c r="B28" s="5"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="20" t="s">
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="F28" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="G28" s="19"/>
-      <c r="H28" s="5" t="s">
-        <v>294</v>
+      <c r="G28" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>305</v>
       </c>
       <c r="I28" s="5"/>
     </row>
-    <row r="29" spans="1:9" hidden="1">
+    <row r="29" spans="1:9">
       <c r="A29" s="5" t="s">
         <v>180</v>
       </c>
       <c r="B29" s="5"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="20" t="s">
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="F29" s="20" t="s">
+      <c r="F29" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G29" s="19"/>
+      <c r="G29" s="18"/>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
     </row>
-    <row r="30" spans="1:9" hidden="1">
+    <row r="30" spans="1:9">
       <c r="A30" s="5" t="s">
         <v>181</v>
       </c>
       <c r="B30" s="5"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="20" t="s">
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="F30" s="20" t="s">
+      <c r="F30" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G30" s="19"/>
+      <c r="G30" s="18"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
     </row>
-    <row r="31" spans="1:9" hidden="1">
+    <row r="31" spans="1:9" ht="27">
       <c r="A31" s="5" t="s">
         <v>182</v>
       </c>
       <c r="B31" s="5"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="20" t="s">
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="F31" s="20" t="s">
+      <c r="F31" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="G31" s="19"/>
-      <c r="H31" s="5" t="s">
-        <v>294</v>
+      <c r="G31" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>305</v>
       </c>
       <c r="I31" s="5"/>
     </row>
-    <row r="32" spans="1:9" hidden="1">
+    <row r="32" spans="1:9" ht="27">
       <c r="A32" s="5" t="s">
         <v>183</v>
       </c>
       <c r="B32" s="5"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="20" t="s">
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="F32" s="20" t="s">
+      <c r="F32" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="G32" s="19"/>
-      <c r="H32" s="5" t="s">
-        <v>294</v>
+      <c r="G32" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>305</v>
       </c>
       <c r="I32" s="5"/>
     </row>
-    <row r="33" spans="1:9" hidden="1">
+    <row r="33" spans="1:9" ht="27">
       <c r="A33" s="5" t="s">
         <v>184</v>
       </c>
       <c r="B33" s="5"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="20" t="s">
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="F33" s="20" t="s">
+      <c r="F33" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="G33" s="19"/>
-      <c r="H33" s="5" t="s">
-        <v>294</v>
+      <c r="G33" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>305</v>
       </c>
       <c r="I33" s="5"/>
     </row>
-    <row r="34" spans="1:9" hidden="1">
+    <row r="34" spans="1:9" ht="27">
       <c r="A34" s="5" t="s">
         <v>185</v>
       </c>
       <c r="B34" s="5"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="20" t="s">
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="F34" s="20" t="s">
+      <c r="F34" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="G34" s="19"/>
-      <c r="H34" s="5" t="s">
-        <v>294</v>
+      <c r="G34" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>305</v>
       </c>
       <c r="I34" s="5"/>
     </row>
-    <row r="35" spans="1:9" hidden="1">
+    <row r="35" spans="1:9" ht="27">
       <c r="A35" s="5" t="s">
         <v>186</v>
       </c>
       <c r="B35" s="5"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="20" t="s">
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="F35" s="20" t="s">
+      <c r="F35" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="G35" s="19"/>
-      <c r="H35" s="5" t="s">
-        <v>294</v>
+      <c r="G35" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>305</v>
       </c>
       <c r="I35" s="5"/>
     </row>
-    <row r="36" spans="1:9" hidden="1">
+    <row r="36" spans="1:9" ht="27">
       <c r="A36" s="5" t="s">
         <v>187</v>
       </c>
       <c r="B36" s="5"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="20" t="s">
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="F36" s="20" t="s">
+      <c r="F36" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="G36" s="19"/>
-      <c r="H36" s="5" t="s">
-        <v>294</v>
+      <c r="G36" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>305</v>
       </c>
       <c r="I36" s="5"/>
     </row>
@@ -3432,19 +3497,19 @@
         <v>188</v>
       </c>
       <c r="B37" s="5"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="20" t="s">
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F37" s="20" t="s">
+      <c r="F37" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="G37" s="19" t="s">
-        <v>302</v>
+      <c r="G37" s="18" t="s">
+        <v>292</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="I37" s="5"/>
     </row>
@@ -3453,19 +3518,19 @@
         <v>189</v>
       </c>
       <c r="B38" s="5"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="20" t="s">
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F38" s="20" t="s">
+      <c r="F38" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="G38" s="19" t="s">
-        <v>302</v>
+      <c r="G38" s="18" t="s">
+        <v>292</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="I38" s="5"/>
     </row>
@@ -3474,19 +3539,19 @@
         <v>190</v>
       </c>
       <c r="B39" s="5"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="20" t="s">
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F39" s="20" t="s">
+      <c r="F39" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="G39" s="19" t="s">
-        <v>302</v>
+      <c r="G39" s="18" t="s">
+        <v>292</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="I39" s="5"/>
     </row>
@@ -3495,19 +3560,19 @@
         <v>191</v>
       </c>
       <c r="B40" s="5"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="20" t="s">
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F40" s="20" t="s">
+      <c r="F40" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="G40" s="19" t="s">
-        <v>302</v>
+      <c r="G40" s="18" t="s">
+        <v>292</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="I40" s="5"/>
     </row>
@@ -3516,19 +3581,19 @@
         <v>192</v>
       </c>
       <c r="B41" s="5"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="20" t="s">
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F41" s="20" t="s">
+      <c r="F41" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="G41" s="19" t="s">
-        <v>302</v>
+      <c r="G41" s="18" t="s">
+        <v>292</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="I41" s="5"/>
     </row>
@@ -3537,17 +3602,17 @@
         <v>193</v>
       </c>
       <c r="B42" s="5"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="20" t="s">
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F42" s="20" t="s">
+      <c r="F42" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G42" s="19"/>
+      <c r="G42" s="18"/>
       <c r="H42" s="5" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="I42" s="5"/>
     </row>
@@ -3556,17 +3621,17 @@
         <v>194</v>
       </c>
       <c r="B43" s="5"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="20" t="s">
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F43" s="20" t="s">
+      <c r="F43" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G43" s="19"/>
+      <c r="G43" s="18"/>
       <c r="H43" s="5" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="I43" s="5"/>
     </row>
@@ -3575,17 +3640,17 @@
         <v>195</v>
       </c>
       <c r="B44" s="5"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="20" t="s">
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F44" s="20" t="s">
+      <c r="F44" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G44" s="19"/>
+      <c r="G44" s="18"/>
       <c r="H44" s="5" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="I44" s="5"/>
     </row>
@@ -3594,34 +3659,34 @@
         <v>196</v>
       </c>
       <c r="B45" s="5"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="20" t="s">
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F45" s="20" t="s">
+      <c r="F45" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G45" s="19"/>
+      <c r="G45" s="18"/>
       <c r="H45" s="5" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="I45" s="5"/>
     </row>
-    <row r="46" spans="1:9" hidden="1">
+    <row r="46" spans="1:9">
       <c r="A46" s="5" t="s">
         <v>197</v>
       </c>
       <c r="B46" s="5"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="20" t="s">
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="F46" s="20" t="s">
+      <c r="F46" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G46" s="19"/>
+      <c r="G46" s="18"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
     </row>
@@ -3630,19 +3695,19 @@
         <v>198</v>
       </c>
       <c r="B47" s="5"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="20" t="s">
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F47" s="20" t="s">
+      <c r="F47" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="G47" s="19" t="s">
-        <v>302</v>
+      <c r="G47" s="18" t="s">
+        <v>292</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="I47" s="5"/>
     </row>
@@ -3651,19 +3716,19 @@
         <v>199</v>
       </c>
       <c r="B48" s="5"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="20" t="s">
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F48" s="20" t="s">
+      <c r="F48" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="G48" s="19" t="s">
-        <v>302</v>
+      <c r="G48" s="18" t="s">
+        <v>292</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="I48" s="5"/>
     </row>
@@ -3672,15 +3737,15 @@
         <v>200</v>
       </c>
       <c r="B49" s="5"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="20" t="s">
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F49" s="20" t="s">
+      <c r="F49" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G49" s="19"/>
+      <c r="G49" s="18"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
     </row>
@@ -3689,15 +3754,15 @@
         <v>201</v>
       </c>
       <c r="B50" s="5"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="19"/>
-      <c r="E50" s="20" t="s">
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F50" s="20" t="s">
+      <c r="F50" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G50" s="19"/>
+      <c r="G50" s="18"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
     </row>
@@ -3706,15 +3771,15 @@
         <v>202</v>
       </c>
       <c r="B51" s="5"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="20" t="s">
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F51" s="20" t="s">
+      <c r="F51" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G51" s="19"/>
+      <c r="G51" s="18"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
     </row>
@@ -3723,15 +3788,15 @@
         <v>203</v>
       </c>
       <c r="B52" s="5"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="20" t="s">
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F52" s="20" t="s">
+      <c r="F52" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G52" s="19"/>
+      <c r="G52" s="18"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
     </row>
@@ -3740,15 +3805,15 @@
         <v>204</v>
       </c>
       <c r="B53" s="5"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="20" t="s">
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F53" s="20" t="s">
+      <c r="F53" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G53" s="19"/>
+      <c r="G53" s="18"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
     </row>
@@ -3757,207 +3822,207 @@
         <v>205</v>
       </c>
       <c r="B54" s="5"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="20" t="s">
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F54" s="20" t="s">
+      <c r="F54" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G54" s="19"/>
+      <c r="G54" s="18"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
     </row>
-    <row r="55" spans="1:9" hidden="1">
+    <row r="55" spans="1:9">
       <c r="A55" s="5" t="s">
         <v>206</v>
       </c>
       <c r="B55" s="5"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="20" t="s">
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="F55" s="21" t="s">
+      <c r="F55" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="G55" s="19"/>
+      <c r="G55" s="18"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
     </row>
-    <row r="56" spans="1:9" hidden="1">
+    <row r="56" spans="1:9">
       <c r="A56" s="5" t="s">
         <v>207</v>
       </c>
       <c r="B56" s="5"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="19"/>
-      <c r="E56" s="20" t="s">
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="F56" s="21" t="s">
+      <c r="F56" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="G56" s="19"/>
+      <c r="G56" s="18"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
     </row>
-    <row r="57" spans="1:9" hidden="1">
+    <row r="57" spans="1:9">
       <c r="A57" s="5" t="s">
         <v>208</v>
       </c>
       <c r="B57" s="5"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="20" t="s">
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="F57" s="20" t="s">
+      <c r="F57" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="G57" s="19" t="s">
-        <v>295</v>
-      </c>
-      <c r="H57" s="12" t="s">
-        <v>298</v>
+      <c r="G57" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>299</v>
       </c>
       <c r="I57" s="5"/>
     </row>
-    <row r="58" spans="1:9" hidden="1">
+    <row r="58" spans="1:9">
       <c r="A58" s="5" t="s">
         <v>209</v>
       </c>
       <c r="B58" s="5"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="20" t="s">
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="F58" s="20" t="s">
+      <c r="F58" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="G58" s="19" t="s">
-        <v>295</v>
-      </c>
-      <c r="H58" s="12" t="s">
-        <v>298</v>
+      <c r="G58" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>299</v>
       </c>
       <c r="I58" s="5"/>
     </row>
-    <row r="59" spans="1:9" hidden="1">
+    <row r="59" spans="1:9">
       <c r="A59" s="5" t="s">
         <v>210</v>
       </c>
       <c r="B59" s="5"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="20" t="s">
+      <c r="C59" s="18"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="F59" s="20" t="s">
+      <c r="F59" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G59" s="19"/>
+      <c r="G59" s="18"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
     </row>
-    <row r="60" spans="1:9" hidden="1">
+    <row r="60" spans="1:9">
       <c r="A60" s="5" t="s">
         <v>211</v>
       </c>
       <c r="B60" s="5"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="20" t="s">
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="F60" s="20" t="s">
+      <c r="F60" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="G60" s="19"/>
+      <c r="G60" s="18"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
     </row>
-    <row r="61" spans="1:9" hidden="1">
+    <row r="61" spans="1:9">
       <c r="A61" s="5" t="s">
         <v>212</v>
       </c>
       <c r="B61" s="5"/>
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="20" t="s">
+      <c r="C61" s="18"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="F61" s="20" t="s">
+      <c r="F61" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="G61" s="19"/>
-      <c r="H61" s="5" t="s">
-        <v>294</v>
+      <c r="G61" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H61" s="11" t="s">
+        <v>299</v>
       </c>
       <c r="I61" s="5"/>
     </row>
-    <row r="62" spans="1:9" hidden="1">
+    <row r="62" spans="1:9" ht="27">
       <c r="A62" s="5" t="s">
         <v>213</v>
       </c>
       <c r="B62" s="5"/>
-      <c r="C62" s="19"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="20" t="s">
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="F62" s="20" t="s">
+      <c r="F62" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="G62" s="19"/>
-      <c r="H62" s="5" t="s">
-        <v>294</v>
+      <c r="G62" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="H62" s="11" t="s">
+        <v>305</v>
       </c>
       <c r="I62" s="5"/>
     </row>
-    <row r="63" spans="1:9" hidden="1">
+    <row r="63" spans="1:9">
       <c r="A63" s="5" t="s">
         <v>214</v>
       </c>
       <c r="B63" s="5"/>
-      <c r="C63" s="19"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="20" t="s">
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="F63" s="20" t="s">
+      <c r="F63" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="G63" s="19"/>
+      <c r="G63" s="18"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
     </row>
-    <row r="64" spans="1:9" hidden="1">
+    <row r="64" spans="1:9">
       <c r="A64" s="5" t="s">
         <v>215</v>
       </c>
       <c r="B64" s="5"/>
-      <c r="C64" s="19"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="20" t="s">
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="F64" s="20" t="s">
+      <c r="F64" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="G64" s="19"/>
+      <c r="G64" s="18"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I64">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="黄晓妮"/>
-      </filters>
-    </filterColumn>
+    <filterColumn colId="4"/>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4420,8 +4485,8 @@
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="11" t="s">
-        <v>246</v>
+      <c r="A13" s="10" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
